--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.5965967476061</v>
+        <v>567.1402026274319</v>
       </c>
       <c r="E2" t="n">
-        <v>10189.90929741433</v>
+        <v>10216.99706558622</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6161701040511955</v>
+        <v>0.6187024935612875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004877731303967</v>
+        <v>0.5004760580870867</v>
       </c>
       <c r="H2" t="n">
-        <v>1.231139174883817</v>
+        <v>1.236227954492138</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.0830040408935</v>
+        <v>223.3206411038572</v>
       </c>
       <c r="E3" t="n">
-        <v>4153.761976719707</v>
+        <v>4173.29798336241</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2514301707758702</v>
+        <v>0.253342455506276</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999452078704735</v>
+        <v>0.599939153500969</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4190885558838454</v>
+        <v>0.422280249635127</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907261899833899</v>
+        <v>0.8907245752344786</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06773219625893</v>
+        <v>1.067744478549455</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.13879870720659</v>
+        <v>37.17264242401994</v>
       </c>
       <c r="E4" t="n">
-        <v>1779.595385371064</v>
+        <v>1769.371404082516</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7669077532057949</v>
+        <v>0.772372155836498</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11265978745663</v>
+        <v>1.112639365921529</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6892562864690464</v>
+        <v>0.6941801445222019</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4736066910350373</v>
+        <v>0.4735850144979386</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052899088601286</v>
+        <v>1.052856219046616</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.46449145578728</v>
+        <v>36.5250023408752</v>
       </c>
       <c r="E5" t="n">
-        <v>360.7682020280016</v>
+        <v>363.0595959154859</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3518014138248498</v>
+        <v>-0.3499374526232535</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634090557495307</v>
+        <v>0.5634011218433819</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6244156181636645</v>
+        <v>-0.6211160025352799</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366560326432893</v>
+        <v>0.7366368760298079</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292683698700809</v>
+        <v>0.8292545380346262</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.29604683103656</v>
+        <v>11.22124060658051</v>
       </c>
       <c r="E6" t="n">
-        <v>1529.402140068162</v>
+        <v>1526.359922377138</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4629415321731214</v>
+        <v>-0.4671236174356096</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8156414217091932</v>
+        <v>0.8158281375578026</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5675797229657832</v>
+        <v>-0.5725760070423083</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.669871193077217</v>
+        <v>0.6697277662458139</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091684395936646</v>
+        <v>1.091726062372388</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.59528596270128</v>
+        <v>10.56737481927993</v>
       </c>
       <c r="E7" t="n">
-        <v>177.1783275604325</v>
+        <v>179.2656695458319</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3290780280359775</v>
+        <v>-0.3305879160494865</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169115907118367</v>
+        <v>0.7169251469322787</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4590217710237171</v>
+        <v>-0.4611191523467568</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511377039229987</v>
+        <v>0.7511456616472796</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075949014288454</v>
+        <v>1.076005945024275</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.485173262394822</v>
+        <v>9.470529088800456</v>
       </c>
       <c r="E8" t="n">
-        <v>352.7458869688647</v>
+        <v>370.060013906752</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3604611671979394</v>
+        <v>-0.3608325729481372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.172136628964337</v>
+        <v>1.172133282169166</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3075248723490807</v>
+        <v>-0.3078426134956047</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7394062879317036</v>
+        <v>0.7394473022962683</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731681052566883</v>
+        <v>1.731812699981029</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.332750609943411</v>
+        <v>7.330556010377784</v>
       </c>
       <c r="E9" t="n">
-        <v>214.6520815484387</v>
+        <v>217.2170744369154</v>
       </c>
       <c r="F9" t="n">
-        <v>0.417555720907937</v>
+        <v>0.4173194772091404</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4815613544312845</v>
+        <v>0.481562563710965</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8670872715711646</v>
+        <v>0.8665945168022167</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.678870413758574</v>
+        <v>0.6788644880406949</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653198286719645</v>
+        <v>0.6532095152018699</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.566195866794694</v>
+        <v>6.570972679871563</v>
       </c>
       <c r="E10" t="n">
-        <v>368.8503709365882</v>
+        <v>375.6889645151488</v>
       </c>
       <c r="F10" t="n">
-        <v>0.934191033139212</v>
+        <v>0.9406844128028362</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8243630321414328</v>
+        <v>0.8243498075118239</v>
       </c>
       <c r="H10" t="n">
-        <v>1.13322771244664</v>
+        <v>1.141122863414199</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6643353131209291</v>
+        <v>0.6643187276823397</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094239464947552</v>
+        <v>1.094220205826798</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.562075791990205</v>
+        <v>6.54336120538993</v>
       </c>
       <c r="E11" t="n">
-        <v>243.0172853586027</v>
+        <v>249.4155768324209</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.289602351838549</v>
+        <v>-0.2889133431230353</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9616626350416873</v>
+        <v>0.9616545763375248</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3011475555832477</v>
+        <v>-0.3004335966697791</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.713595918169725</v>
+        <v>0.7135849464572159</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371139452078677</v>
+        <v>1.37113897513703</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.220990283809562</v>
+        <v>6.343000222334977</v>
       </c>
       <c r="E12" t="n">
-        <v>94.9659682749064</v>
+        <v>95.54412454661946</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2913287558475609</v>
+        <v>-0.2886991105935401</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6607308576659394</v>
+        <v>0.6607038931862791</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4409189497773608</v>
+        <v>-0.4369568782185823</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,45 +1084,45 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890964113748042</v>
+        <v>0.7890824253289996</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041744427456671</v>
+        <v>1.041707834041929</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>BCH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.58004379110498</v>
+        <v>4.582709057123902</v>
       </c>
       <c r="E13" t="n">
-        <v>138.1333162273361</v>
+        <v>199.0865898079189</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.403080532479396</v>
+        <v>1.657447455453443</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8534357378492193</v>
+        <v>0.8637948445486034</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4723033201014254</v>
+        <v>1.918797577820207</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4691011235955056</v>
+        <v>0.3000688231245698</v>
       </c>
       <c r="J13" t="n">
         <v>268</v>
@@ -1138,45 +1138,45 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7602475849185201</v>
+        <v>0.6040268045114212</v>
       </c>
       <c r="N13" t="n">
-        <v>1.296380238272036</v>
+        <v>1.042517881275638</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BCH</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.572303542455347</v>
+        <v>4.565119191959193</v>
       </c>
       <c r="E14" t="n">
-        <v>197.9976233568074</v>
+        <v>137.610954158833</v>
       </c>
       <c r="F14" t="n">
-        <v>1.640570716091748</v>
+        <v>-0.403080532479396</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8638806765175828</v>
+        <v>0.8534357378492193</v>
       </c>
       <c r="H14" t="n">
-        <v>1.899070972052652</v>
+        <v>-0.4723033201014254</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3000688231245698</v>
+        <v>0.4691011235955056</v>
       </c>
       <c r="J14" t="n">
         <v>268</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.6040498996959536</v>
+        <v>0.7602315674030167</v>
       </c>
       <c r="N14" t="n">
-        <v>1.042636931439606</v>
+        <v>1.296383269846575</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.946603291216095</v>
+        <v>3.966345227792499</v>
       </c>
       <c r="E15" t="n">
-        <v>220.0201770102807</v>
+        <v>223.7844478851851</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.09309805442537211</v>
+        <v>-0.08345734852079323</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7940309721035923</v>
+        <v>0.7939334454123167</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1172473841652945</v>
+        <v>-0.1051188219907413</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7171922586543213</v>
+        <v>0.7171689691632496</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137835721265646</v>
+        <v>1.137685652350429</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.926129451501701</v>
+        <v>3.894858430344999</v>
       </c>
       <c r="E16" t="n">
-        <v>188.9499589649328</v>
+        <v>189.4967478584616</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4148530221746605</v>
+        <v>0.4054681295116238</v>
       </c>
       <c r="G16" t="n">
-        <v>0.960402952279271</v>
+        <v>0.9604938594589956</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4319572541818128</v>
+        <v>0.4221454676868068</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5159194731140123</v>
+        <v>0.5158909525418903</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9900153644472122</v>
+        <v>0.9900775153178559</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.328965899427971</v>
+        <v>3.336087510367359</v>
       </c>
       <c r="E17" t="n">
-        <v>54.63251515220437</v>
+        <v>55.64137586286316</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2266527799835046</v>
+        <v>-0.2228122659968633</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559479762789919</v>
+        <v>0.7559266779087533</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.299825896881369</v>
+        <v>-0.2947538068285488</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244788203665578</v>
+        <v>0.7244537445435394</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094269086110924</v>
+        <v>1.094225994555092</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.082345873363124</v>
+        <v>3.086701475669568</v>
       </c>
       <c r="E18" t="n">
-        <v>57.02306054497093</v>
+        <v>58.41887735298038</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4780876705917633</v>
+        <v>-0.4764866283356513</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7485132366481742</v>
+        <v>0.7484894084456359</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6387163876121007</v>
+        <v>-0.636597689906068</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645716353882039</v>
+        <v>0.7645589454582185</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143468472514927</v>
+        <v>1.143439858032655</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.965683758004008</v>
+        <v>2.956601239757834</v>
       </c>
       <c r="E19" t="n">
-        <v>80.52229877448879</v>
+        <v>79.65194724754794</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1136156586017614</v>
+        <v>0.1117424789995929</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4830425255180984</v>
+        <v>0.48306778983837</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2352083980181668</v>
+        <v>0.2313184222797816</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177577373709445</v>
+        <v>0.7177157889887283</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6927392211827045</v>
+        <v>0.6927511802343952</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.559062741232973</v>
+        <v>2.555568081346226</v>
       </c>
       <c r="E20" t="n">
-        <v>99.98929090521492</v>
+        <v>100.4583067288582</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3346442461826112</v>
+        <v>-0.3341402050199824</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7811071712279219</v>
+        <v>0.781102426302225</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4284229597540902</v>
+        <v>-0.4277802676939791</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328615476311175</v>
+        <v>0.7328562591331287</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143771019202731</v>
+        <v>1.143782590375283</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.1402026274319</v>
+        <v>568.7251975399789</v>
       </c>
       <c r="E2" t="n">
-        <v>10216.99706558622</v>
+        <v>10571.23218100073</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6187024935612875</v>
+        <v>0.6222139318833635</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004760580870867</v>
+        <v>0.500465661357778</v>
       </c>
       <c r="H2" t="n">
-        <v>1.236227954492138</v>
+        <v>1.243269978194466</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.3206411038572</v>
+        <v>223.8673135119022</v>
       </c>
       <c r="E3" t="n">
-        <v>4173.29798336241</v>
+        <v>4239.0651271718</v>
       </c>
       <c r="F3" t="n">
-        <v>0.253342455506276</v>
+        <v>0.2561939346256328</v>
       </c>
       <c r="G3" t="n">
-        <v>0.599939153500969</v>
+        <v>0.5999353395256627</v>
       </c>
       <c r="H3" t="n">
-        <v>0.422280249635127</v>
+        <v>0.4270359116170617</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907245752344786</v>
+        <v>0.8907232914459278</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067744478549455</v>
+        <v>1.067758332963844</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.17264242401994</v>
+        <v>37.47573274614552</v>
       </c>
       <c r="E4" t="n">
-        <v>1769.371404082516</v>
+        <v>1762.572796331772</v>
       </c>
       <c r="F4" t="n">
-        <v>0.772372155836498</v>
+        <v>0.7846834352216048</v>
       </c>
       <c r="G4" t="n">
-        <v>1.112639365921529</v>
+        <v>1.112615903159633</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6941801445222019</v>
+        <v>0.7052599490922631</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735850144979386</v>
+        <v>0.4735603145657332</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052856219046616</v>
+        <v>1.052800976717649</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.5250023408752</v>
+        <v>36.61805239997795</v>
       </c>
       <c r="E5" t="n">
-        <v>363.0595959154859</v>
+        <v>360.6551127835849</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3499374526232535</v>
+        <v>-0.3473255193471501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634011218433819</v>
+        <v>0.5634077374082593</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6211160025352799</v>
+        <v>-0.6164727537198682</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366368760298079</v>
+        <v>0.7366164844347561</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292545380346262</v>
+        <v>0.8292585463447444</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.22124060658051</v>
+        <v>11.19363796696501</v>
       </c>
       <c r="E6" t="n">
-        <v>1526.359922377138</v>
+        <v>1480.820767686679</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4671236174356096</v>
+        <v>-0.468213165968402</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8158281375578026</v>
+        <v>0.8158853913081215</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5725760070423083</v>
+        <v>-0.5738712458347963</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6697277662458139</v>
+        <v>0.6695823776189148</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091726062372388</v>
+        <v>1.091588339336801</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.56737481927993</v>
+        <v>10.65027535646747</v>
       </c>
       <c r="E7" t="n">
-        <v>179.2656695458319</v>
+        <v>181.0031441907302</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3305879160494865</v>
+        <v>-0.3260555422844575</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169251469322787</v>
+        <v>0.7168997140151837</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4611191523467568</v>
+        <v>-0.454813324528055</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511456616472796</v>
+        <v>0.7511265023559583</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076005945024275</v>
+        <v>1.075962680970545</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.470529088800456</v>
+        <v>9.544548992353139</v>
       </c>
       <c r="E8" t="n">
-        <v>370.060013906752</v>
+        <v>376.7471210346181</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3608325729481372</v>
+        <v>-0.3548832101478316</v>
       </c>
       <c r="G8" t="n">
-        <v>1.172133282169166</v>
+        <v>1.172212225121037</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3078426134956047</v>
+        <v>-0.3027465526655705</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7394473022962683</v>
+        <v>0.7394109782244725</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731812699981029</v>
+        <v>1.731880236721781</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.330556010377784</v>
+        <v>7.339923790870295</v>
       </c>
       <c r="E9" t="n">
-        <v>217.2170744369154</v>
+        <v>220.1055128028705</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4173194772091404</v>
+        <v>0.4196823849581928</v>
       </c>
       <c r="G9" t="n">
-        <v>0.481562563710965</v>
+        <v>0.4815523421910195</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8665945168022167</v>
+        <v>0.871519766778988</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788644880406949</v>
+        <v>0.6788498253602014</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532095152018699</v>
+        <v>0.6531951113514475</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.570972679871563</v>
+        <v>6.597054852757689</v>
       </c>
       <c r="E10" t="n">
-        <v>375.6889645151488</v>
+        <v>375.5090006931899</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9406844128028362</v>
+        <v>0.9451150310403937</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8243498075118239</v>
+        <v>0.8243464420711555</v>
       </c>
       <c r="H10" t="n">
-        <v>1.141122863414199</v>
+        <v>1.146502226255516</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6643187276823397</v>
+        <v>0.6643155621600689</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094220205826798</v>
+        <v>1.094233255870995</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.54336120538993</v>
+        <v>6.573811713828974</v>
       </c>
       <c r="E11" t="n">
-        <v>249.4155768324209</v>
+        <v>252.4992967576971</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2889133431230353</v>
+        <v>-0.2869831748520146</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9616545763375248</v>
+        <v>0.9616357179280421</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3004335966697791</v>
+        <v>-0.298432316418481</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7135849464572159</v>
+        <v>0.7135700207386202</v>
       </c>
       <c r="N11" t="n">
-        <v>1.37113897513703</v>
+        <v>1.371111890720424</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.343000222334977</v>
+        <v>6.383175617148461</v>
       </c>
       <c r="E12" t="n">
-        <v>95.54412454661946</v>
+        <v>94.7240405460916</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2886991105935401</v>
+        <v>-0.2841851331092454</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6607038931862791</v>
+        <v>0.6606922855580479</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4369568782185823</v>
+        <v>-0.4301323616473151</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890824253289996</v>
+        <v>0.789058827024346</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041707834041929</v>
+        <v>1.041680019468464</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.582709057123902</v>
+        <v>4.63432709320483</v>
       </c>
       <c r="E13" t="n">
-        <v>199.0865898079189</v>
+        <v>204.9696898333766</v>
       </c>
       <c r="F13" t="n">
-        <v>1.657447455453443</v>
+        <v>1.694368351991063</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8637948445486034</v>
+        <v>0.8637237457538678</v>
       </c>
       <c r="H13" t="n">
-        <v>1.918797577820207</v>
+        <v>1.961701713447972</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040268045114212</v>
+        <v>0.60399012231334</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042517881275638</v>
+        <v>1.042390419809183</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.565119191959193</v>
+        <v>4.5984384746684</v>
       </c>
       <c r="E14" t="n">
-        <v>137.610954158833</v>
+        <v>137.8776618096302</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.403080532479396</v>
+        <v>-0.3981480525630399</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8534357378492193</v>
+        <v>0.8533755476112839</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4723033201014254</v>
+        <v>-0.4665566686056465</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602315674030167</v>
+        <v>0.7602231309562866</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296383269846575</v>
+        <v>1.296304383654399</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.966345227792499</v>
+        <v>3.997377116616702</v>
       </c>
       <c r="E15" t="n">
-        <v>223.7844478851851</v>
+        <v>227.4253834465834</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.08345734852079323</v>
+        <v>-0.07294028624838622</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7939334454123167</v>
+        <v>0.7939415840796668</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1051188219907413</v>
+        <v>-0.09187109947508071</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7171689691632496</v>
+        <v>0.7171105136333313</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137685652350429</v>
+        <v>1.137628215309686</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.894858430344999</v>
+        <v>3.923965410327336</v>
       </c>
       <c r="E16" t="n">
-        <v>189.4967478584616</v>
+        <v>190.4847370583887</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4054681295116238</v>
+        <v>0.4161950752055421</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9604938594589956</v>
+        <v>0.9603926295024391</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4221454676868068</v>
+        <v>0.4333592974585454</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158909525418903</v>
+        <v>0.5158602045817712</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9900775153178559</v>
+        <v>0.9899347279688316</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.336087510367359</v>
+        <v>3.381687028031335</v>
       </c>
       <c r="E17" t="n">
-        <v>55.64137586286316</v>
+        <v>57.81665807912396</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2228122659968633</v>
+        <v>-0.2107092558862034</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559266779087533</v>
+        <v>0.7560118116411305</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2947538068285488</v>
+        <v>-0.2787115923874275</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244537445435394</v>
+        <v>0.7243123792501396</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094225994555092</v>
+        <v>1.094158413477103</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.086701475669568</v>
+        <v>3.101285132178825</v>
       </c>
       <c r="E18" t="n">
-        <v>58.41887735298038</v>
+        <v>59.13405336504969</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4764866283356513</v>
+        <v>-0.4736816718550733</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7484894084456359</v>
+        <v>0.748469248448891</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.636597689906068</v>
+        <v>-0.6328672458310336</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645589454582185</v>
+        <v>0.7645448876920352</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143439858032655</v>
+        <v>1.143411789619691</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.956601239757834</v>
+        <v>2.974533080926777</v>
       </c>
       <c r="E19" t="n">
-        <v>79.65194724754794</v>
+        <v>79.27955442161525</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1117424789995929</v>
+        <v>0.1201783798954763</v>
       </c>
       <c r="G19" t="n">
-        <v>0.48306778983837</v>
+        <v>0.4829871053008384</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2313184222797816</v>
+        <v>0.2488231643795557</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177157889887283</v>
+        <v>0.7177293966006381</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6927511802343952</v>
+        <v>0.6926629945258923</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.555568081346226</v>
+        <v>2.574114422642796</v>
       </c>
       <c r="E20" t="n">
-        <v>100.4583067288582</v>
+        <v>100.7001828969736</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3341402050199824</v>
+        <v>-0.3290942213196093</v>
       </c>
       <c r="G20" t="n">
-        <v>0.781102426302225</v>
+        <v>0.7810839118196563</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4277802676939791</v>
+        <v>-0.4213301750805918</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328562591331287</v>
+        <v>0.7328319143090687</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143782590375283</v>
+        <v>1.143741244467937</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.7251975399789</v>
+        <v>567.8557141656451</v>
       </c>
       <c r="E2" t="n">
-        <v>10571.23218100073</v>
+        <v>10658.93480837871</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6222139318833635</v>
+        <v>0.621418070492177</v>
       </c>
       <c r="G2" t="n">
-        <v>0.500465661357778</v>
+        <v>0.5004674227650846</v>
       </c>
       <c r="H2" t="n">
-        <v>1.243269978194466</v>
+        <v>1.24167536631823</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.8673135119022</v>
+        <v>223.3361500709903</v>
       </c>
       <c r="E3" t="n">
-        <v>4239.0651271718</v>
+        <v>4248.307908589578</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2561939346256328</v>
+        <v>0.2538850236693857</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999353395256627</v>
+        <v>0.5999379471934543</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4270359116170617</v>
+        <v>0.4231854725260755</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907232914459278</v>
+        <v>0.8907286856615978</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067758332963844</v>
+        <v>1.067765682388836</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.47573274614552</v>
+        <v>37.32996553228262</v>
       </c>
       <c r="E4" t="n">
-        <v>1762.572796331772</v>
+        <v>1754.833443626319</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7846834352216048</v>
+        <v>0.7795509833906926</v>
       </c>
       <c r="G4" t="n">
-        <v>1.112615903159633</v>
+        <v>1.112621895554882</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7052599490922631</v>
+        <v>0.7006432162670304</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735603145657332</v>
+        <v>0.4735674342212019</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052800976717649</v>
+        <v>1.052818769751531</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.61805239997795</v>
+        <v>36.65027379538029</v>
       </c>
       <c r="E5" t="n">
-        <v>360.6551127835849</v>
+        <v>363.9126167417351</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3473255193471501</v>
+        <v>-0.3469521588965258</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634077374082593</v>
+        <v>0.5634103703765341</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6164727537198682</v>
+        <v>-0.6158071933689353</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366164844347561</v>
+        <v>0.7366022934934546</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292585463447444</v>
+        <v>0.8292435273897014</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.19363796696501</v>
+        <v>11.22201841018824</v>
       </c>
       <c r="E6" t="n">
-        <v>1480.820767686679</v>
+        <v>1428.25972465024</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.468213165968402</v>
+        <v>-0.469302121578274</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8158853913081215</v>
+        <v>0.81594617964742</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5738712458347963</v>
+        <v>-0.5751630846302449</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6695823776189148</v>
+        <v>0.6695687677412272</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091588339336801</v>
+        <v>1.091643637923919</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.65027535646747</v>
+        <v>10.60290638489901</v>
       </c>
       <c r="E7" t="n">
-        <v>181.0031441907302</v>
+        <v>179.678524484244</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3260555422844575</v>
+        <v>-0.32877594197574</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7168997140151837</v>
+        <v>0.7169094888829914</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.454813324528055</v>
+        <v>-0.4586017441169625</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511265023559583</v>
+        <v>0.7511362022377871</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075962680970545</v>
+        <v>1.075987459588492</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.544548992353139</v>
+        <v>9.479979435460846</v>
       </c>
       <c r="E8" t="n">
-        <v>376.7471210346181</v>
+        <v>375.2262388069947</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3548832101478316</v>
+        <v>-0.3608325729481372</v>
       </c>
       <c r="G8" t="n">
-        <v>1.172212225121037</v>
+        <v>1.172133282169166</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3027465526655705</v>
+        <v>-0.3078426134956047</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7394109782244725</v>
+        <v>0.7394785905427288</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731880236721781</v>
+        <v>1.731915861052021</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.339923790870295</v>
+        <v>7.349673791797612</v>
       </c>
       <c r="E9" t="n">
-        <v>220.1055128028705</v>
+        <v>220.3815189266446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4196823849581928</v>
+        <v>0.4225192544024443</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4815523421910195</v>
+        <v>0.4815455656582007</v>
       </c>
       <c r="H9" t="n">
-        <v>0.871519766778988</v>
+        <v>0.8774232067217226</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788498253602014</v>
+        <v>0.6788454419055356</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531951113514475</v>
+        <v>0.6531794027886894</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.597054852757689</v>
+        <v>6.579163820897458</v>
       </c>
       <c r="E10" t="n">
-        <v>375.5090006931899</v>
+        <v>379.0268638559825</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9451150310403937</v>
+        <v>0.9418656484365191</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8243464420711555</v>
+        <v>0.8243484620203013</v>
       </c>
       <c r="H10" t="n">
-        <v>1.146502226255516</v>
+        <v>1.142557658357497</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6643155621600689</v>
+        <v>0.6643200723359343</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094233255870995</v>
+        <v>1.094239514919229</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.573811713828974</v>
+        <v>6.556884617079429</v>
       </c>
       <c r="E11" t="n">
-        <v>252.4992967576971</v>
+        <v>253.8712697692924</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2869831748520146</v>
+        <v>-0.2893267696535436</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9616357179280421</v>
+        <v>0.9616593279691075</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.298432316418481</v>
+        <v>-0.3008620217562513</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7135700207386202</v>
+        <v>0.7135692761528079</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371111890720424</v>
+        <v>1.371139297685342</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.383175617148461</v>
+        <v>6.257339607890875</v>
       </c>
       <c r="E12" t="n">
-        <v>94.7240405460916</v>
+        <v>96.0483316832626</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2841851331092454</v>
+        <v>-0.2845615876279169</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6606922855580479</v>
+        <v>0.6606915826609705</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4301323616473151</v>
+        <v>-0.4307026078368216</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.789058827024346</v>
+        <v>0.7890584401427911</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041680019468464</v>
+        <v>1.041674734290633</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.63432709320483</v>
+        <v>4.623267247575432</v>
       </c>
       <c r="E13" t="n">
-        <v>204.9696898333766</v>
+        <v>204.3746088419748</v>
       </c>
       <c r="F13" t="n">
-        <v>1.694368351991063</v>
+        <v>1.685125442745689</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8637237457538678</v>
+        <v>0.8637265821116433</v>
       </c>
       <c r="H13" t="n">
-        <v>1.961701713447972</v>
+        <v>1.95099407340907</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.60399012231334</v>
+        <v>0.6040011447081863</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042390419809183</v>
+        <v>1.042409197042181</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.5984384746684</v>
+        <v>4.580581005940749</v>
       </c>
       <c r="E14" t="n">
-        <v>137.8776618096302</v>
+        <v>136.2746988126715</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3981480525630399</v>
+        <v>-0.4018484241161812</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8533755476112839</v>
+        <v>0.8534153757663578</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4665566686056465</v>
+        <v>-0.4708708508507075</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602231309562866</v>
+        <v>0.760217133092645</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296304383654399</v>
+        <v>1.29635009351411</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.997377116616702</v>
+        <v>4.030509726348628</v>
       </c>
       <c r="E15" t="n">
-        <v>227.4253834465834</v>
+        <v>237.3280658337819</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07294028624838622</v>
+        <v>-0.06562750691309538</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7939415840796668</v>
+        <v>0.7940171259539203</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09187109947508071</v>
+        <v>-0.08265250807311174</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7171105136333313</v>
+        <v>0.7169945977768535</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137628215309686</v>
+        <v>1.137548547527522</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.923965410327336</v>
+        <v>3.920369144369439</v>
       </c>
       <c r="E16" t="n">
-        <v>190.4847370583887</v>
+        <v>190.8436494597687</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4161950752055421</v>
+        <v>0.4148530221746605</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9603926295024391</v>
+        <v>0.960402952279271</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4333592974585454</v>
+        <v>0.4319572541818128</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158602045817712</v>
+        <v>0.5158671249003641</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9899347279688316</v>
+        <v>0.9899551643158296</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.381687028031335</v>
+        <v>3.357988691708691</v>
       </c>
       <c r="E17" t="n">
-        <v>57.81665807912396</v>
+        <v>58.18065490435263</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2107092558862034</v>
+        <v>-0.2182336418529588</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7560118116411305</v>
+        <v>0.7559317801486399</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2787115923874275</v>
+        <v>-0.2886948896500253</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7243123792501396</v>
+        <v>0.7244241589337255</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094158413477103</v>
+        <v>1.094207573032178</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.101285132178825</v>
+        <v>3.087316516767466</v>
       </c>
       <c r="E18" t="n">
-        <v>59.13405336504969</v>
+        <v>59.36150543917159</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4736816718550733</v>
+        <v>-0.4769670778386845</v>
       </c>
       <c r="G18" t="n">
-        <v>0.748469248448891</v>
+        <v>0.7484956170543778</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6328672458310336</v>
+        <v>-0.6372342963285957</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645448876920352</v>
+        <v>0.7645493156428754</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143411789619691</v>
+        <v>1.143454670073963</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.974533080926777</v>
+        <v>2.979677021368349</v>
       </c>
       <c r="E19" t="n">
-        <v>79.27955442161525</v>
+        <v>78.06010839839448</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1201783798954763</v>
+        <v>0.122055324032732</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4829871053008384</v>
+        <v>0.4829807026259032</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2488231643795557</v>
+        <v>0.2527126308962928</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177293966006381</v>
+        <v>0.7177277105457881</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926629945258923</v>
+        <v>0.6926497473466916</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.574114422642796</v>
+        <v>2.571618015923029</v>
       </c>
       <c r="E20" t="n">
-        <v>100.7001828969736</v>
+        <v>100.2475196944267</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3290942213196093</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328319143090687</v>
+        <v>0.7328283211572265</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143741244467937</v>
+        <v>1.143731611179012</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.8557141656451</v>
+        <v>568.0764182229543</v>
       </c>
       <c r="E2" t="n">
-        <v>10658.93480837871</v>
+        <v>10657.10016806394</v>
       </c>
       <c r="F2" t="n">
-        <v>0.621418070492177</v>
+        <v>0.6218209009407405</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004674227650846</v>
+        <v>0.5004664876513688</v>
       </c>
       <c r="H2" t="n">
-        <v>1.24167536631823</v>
+        <v>1.242482596305047</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.3361500709903</v>
+        <v>223.3740410633003</v>
       </c>
       <c r="E3" t="n">
-        <v>4248.307908589578</v>
+        <v>4260.927936993562</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2538850236693857</v>
+        <v>0.2531125725672965</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999379471934543</v>
+        <v>0.5999397327741256</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4231854725260755</v>
+        <v>0.421896665181521</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907286856615978</v>
+        <v>0.8907301251615735</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067765682388836</v>
+        <v>1.067772581079508</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.32996553228262</v>
+        <v>37.17927155104492</v>
       </c>
       <c r="E4" t="n">
-        <v>1754.833443626319</v>
+        <v>1747.853617543579</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7795509833906926</v>
+        <v>0.7679319870818961</v>
       </c>
       <c r="G4" t="n">
-        <v>1.112621895554882</v>
+        <v>1.112655489988379</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7006432162670304</v>
+        <v>0.6901794796248358</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735674342212019</v>
+        <v>0.4735735731049171</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052818769751531</v>
+        <v>1.052866173919842</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.65027379538029</v>
+        <v>36.57581036235815</v>
       </c>
       <c r="E5" t="n">
-        <v>363.9126167417351</v>
+        <v>362.9372154218605</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3469521588965258</v>
+        <v>-0.3491914700321407</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634103703765341</v>
+        <v>0.5634009021169566</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6158071933689353</v>
+        <v>-0.619792174134027</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366022934934546</v>
+        <v>0.7366403905673928</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292435273897014</v>
+        <v>0.8292740289746775</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.22201841018824</v>
+        <v>11.24185591176511</v>
       </c>
       <c r="E6" t="n">
-        <v>1428.25972465024</v>
+        <v>1404.752148100958</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.469302121578274</v>
+        <v>-0.4681223928958503</v>
       </c>
       <c r="G6" t="n">
-        <v>0.81594617964742</v>
+        <v>0.8158804851500326</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5751630846302449</v>
+        <v>-0.573763438905843</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6695687677412272</v>
+        <v>0.6695988780555455</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091643637923919</v>
+        <v>1.09160687271521</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.60290638489901</v>
+        <v>10.56380268148557</v>
       </c>
       <c r="E7" t="n">
-        <v>179.678524484244</v>
+        <v>181.5707218748438</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.32877594197574</v>
+        <v>-0.3320968995500541</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169094888829914</v>
+        <v>0.7169437813859957</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4586017441169625</v>
+        <v>-0.4632119116899854</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511362022377871</v>
+        <v>0.7511241347413222</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075987459588492</v>
+        <v>1.076023651411526</v>
       </c>
     </row>
     <row r="8">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.479979435460846</v>
+        <v>9.479837801150577</v>
       </c>
       <c r="E8" t="n">
-        <v>375.2262388069947</v>
+        <v>375.3690634229048</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3608325729481372</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7394785905427288</v>
+        <v>0.7394827202188133</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731915861052021</v>
+        <v>1.731928769147207</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.349673791797612</v>
+        <v>7.326688739167762</v>
       </c>
       <c r="E9" t="n">
-        <v>220.3815189266446</v>
+        <v>224.1328936004049</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4225192544024443</v>
+        <v>0.4154299044041103</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4815455656582007</v>
+        <v>0.4815737349028132</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8774232067217226</v>
+        <v>0.8626506686207638</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788454419055356</v>
+        <v>0.6788432051866262</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531794027886894</v>
+        <v>0.6532166804400541</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.579163820897458</v>
+        <v>6.577026347170241</v>
       </c>
       <c r="E10" t="n">
-        <v>379.0268638559825</v>
+        <v>379.1625186855754</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9418656484365191</v>
+        <v>0.9415703216209741</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8243484620203013</v>
+        <v>0.8243487678450718</v>
       </c>
       <c r="H10" t="n">
-        <v>1.142557658357497</v>
+        <v>1.142198979786591</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6643200723359343</v>
+        <v>0.6643207658256226</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094239514919229</v>
+        <v>1.09424310772979</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.556884617079429</v>
+        <v>6.55643037871898</v>
       </c>
       <c r="E11" t="n">
-        <v>253.8712697692924</v>
+        <v>255.5841845867208</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2893267696535436</v>
+        <v>-0.2876726802723312</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9616593279691075</v>
+        <v>0.9616418261128674</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3008620217562513</v>
+        <v>-0.2991474293866324</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7135692761528079</v>
+        <v>0.7135707956237323</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371139297685342</v>
+        <v>1.37111982499502</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.257339607890875</v>
+        <v>6.264960691054393</v>
       </c>
       <c r="E12" t="n">
-        <v>96.0483316832626</v>
+        <v>96.88481891718564</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2845615876279169</v>
+        <v>-0.2834320662201184</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6606915826609705</v>
+        <v>0.6606946023696949</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4307026078368216</v>
+        <v>-0.4289910424627967</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890584401427911</v>
+        <v>0.789048258155477</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041674734290633</v>
+        <v>1.041667999827576</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.623267247575432</v>
+        <v>4.624849210071578</v>
       </c>
       <c r="E13" t="n">
-        <v>204.3746088419748</v>
+        <v>201.1243772139795</v>
       </c>
       <c r="F13" t="n">
-        <v>1.685125442745689</v>
+        <v>1.691286444456555</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8637265821116433</v>
+        <v>0.8637235846103802</v>
       </c>
       <c r="H13" t="n">
-        <v>1.95099407340907</v>
+        <v>1.958133915284347</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040011447081863</v>
+        <v>0.6039937058097022</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042409197042181</v>
+        <v>1.042394688827745</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.580581005940749</v>
+        <v>4.572459419509251</v>
       </c>
       <c r="E14" t="n">
-        <v>136.2746988126715</v>
+        <v>136.5142322589455</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4018484241161812</v>
+        <v>-0.4036963333907216</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8534153757663578</v>
+        <v>0.8534472473943604</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4708708508507075</v>
+        <v>-0.4730184960151168</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.760217133092645</v>
+        <v>0.7601985263040427</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29635009351411</v>
+        <v>1.296369199048927</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.030509726348628</v>
+        <v>4.018815210231915</v>
       </c>
       <c r="E15" t="n">
-        <v>237.3280658337819</v>
+        <v>241.0638716002964</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06562750691309538</v>
+        <v>-0.06783995715718083</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7940171259539203</v>
+        <v>0.7939882508939553</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08265250807311174</v>
+        <v>-0.0854420164036426</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7169945977768535</v>
+        <v>0.7170393535387894</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137548547527522</v>
+        <v>1.137580309942735</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.920369144369439</v>
+        <v>3.890220460043761</v>
       </c>
       <c r="E16" t="n">
-        <v>190.8436494597687</v>
+        <v>191.0847108094377</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4148530221746605</v>
+        <v>0.4014511187557093</v>
       </c>
       <c r="G16" t="n">
-        <v>0.960402952279271</v>
+        <v>0.9605428080168004</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4319572541818128</v>
+        <v>0.4179419338785864</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158671249003641</v>
+        <v>0.515822438474443</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9899551643158296</v>
+        <v>0.9900154070565159</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.357988691708691</v>
+        <v>3.344093483246729</v>
       </c>
       <c r="E17" t="n">
-        <v>58.18065490435263</v>
+        <v>58.21168593919104</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2182336418529588</v>
+        <v>-0.2222632086124449</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559317801486399</v>
+        <v>0.7559255421649097</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2886948896500253</v>
+        <v>-0.2940279117648293</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244241589337255</v>
+        <v>0.7244578560392059</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094207573032178</v>
+        <v>1.094251485593087</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.087316516767466</v>
+        <v>3.082584293839066</v>
       </c>
       <c r="E18" t="n">
-        <v>59.36150543917159</v>
+        <v>60.07944859104794</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4769670778386845</v>
+        <v>-0.4784077226028313</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7484956170543778</v>
+        <v>0.7485190763730568</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6372342963285957</v>
+        <v>-0.6391389848351655</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645493156428754</v>
+        <v>0.7645363005994433</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143454670073963</v>
+        <v>1.143473178921461</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.979677021368349</v>
+        <v>2.980531528258254</v>
       </c>
       <c r="E19" t="n">
-        <v>78.06010839839448</v>
+        <v>75.98964820029538</v>
       </c>
       <c r="F19" t="n">
-        <v>0.122055324032732</v>
+        <v>0.122994109176451</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4829807026259032</v>
+        <v>0.4829790733892665</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2527126308962928</v>
+        <v>0.2546572221304534</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177277105457881</v>
+        <v>0.7177239878892615</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926497473466916</v>
+        <v>0.6926451124565257</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.571618015923029</v>
+        <v>2.566973878863285</v>
       </c>
       <c r="E20" t="n">
-        <v>100.2475196944267</v>
+        <v>100.1233473686129</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3290942213196093</v>
+        <v>-0.3311138295212681</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7810839118196563</v>
+        <v>0.7810850044290423</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4213301750805918</v>
+        <v>-0.4239152302806092</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328283211572265</v>
+        <v>0.7328430102929906</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143731611179012</v>
+        <v>1.14375827365936</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.0764182229543</v>
+        <v>568.8405613573444</v>
       </c>
       <c r="E2" t="n">
-        <v>10657.10016806394</v>
+        <v>10626.78926035213</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6218209009407405</v>
+        <v>0.6246520446385311</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004664876513688</v>
+        <v>0.5004624339627352</v>
       </c>
       <c r="H2" t="n">
-        <v>1.242482596305047</v>
+        <v>1.248149715638883</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.3740410633003</v>
+        <v>223.3482538661895</v>
       </c>
       <c r="E3" t="n">
-        <v>4260.927936993562</v>
+        <v>4257.149412857553</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2531125725672965</v>
+        <v>0.2550715341211798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999397327741256</v>
+        <v>0.5999360964357482</v>
       </c>
       <c r="H3" t="n">
-        <v>0.421896665181521</v>
+        <v>0.4251645060808528</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907301251615735</v>
+        <v>0.8907285728537627</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067772581079508</v>
+        <v>1.067772897059166</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.17927155104492</v>
+        <v>37.15924095207325</v>
       </c>
       <c r="E4" t="n">
-        <v>1747.853617543579</v>
+        <v>1733.487929051063</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7679319870818961</v>
+        <v>0.7614478379672653</v>
       </c>
       <c r="G4" t="n">
-        <v>1.112655489988379</v>
+        <v>1.112686358490045</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6901794796248358</v>
+        <v>0.6843328599809355</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735735731049171</v>
+        <v>0.4735424062968398</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052866173919842</v>
+        <v>1.052834618336764</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.57581036235815</v>
+        <v>36.67376664137493</v>
       </c>
       <c r="E5" t="n">
-        <v>362.9372154218605</v>
+        <v>358.9755300470716</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3491914700321407</v>
+        <v>-0.3469521588965258</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634009021169566</v>
+        <v>0.5634103703765341</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.619792174134027</v>
+        <v>-0.6158071933689353</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366403905673928</v>
+        <v>0.7366294062709446</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292740289746775</v>
+        <v>0.8292823166189179</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.24185591176511</v>
+        <v>11.23792335730281</v>
       </c>
       <c r="E6" t="n">
-        <v>1404.752148100958</v>
+        <v>1364.440322426925</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4681223928958503</v>
+        <v>-0.4677592594370329</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8158804851500326</v>
+        <v>0.8158611059843303</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.573763438905843</v>
+        <v>-0.5733319752664087</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6695988780555455</v>
+        <v>0.6695167882144167</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09160687271521</v>
+        <v>1.09145596200406</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.56380268148557</v>
+        <v>10.60445276429337</v>
       </c>
       <c r="E7" t="n">
-        <v>181.5707218748438</v>
+        <v>195.3126156050431</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3320968995500541</v>
+        <v>-0.3290780280359775</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169437813859957</v>
+        <v>0.7169115907118367</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4632119116899854</v>
+        <v>-0.4590217710237171</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511241347413222</v>
+        <v>0.7511243851709059</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076023651411526</v>
+        <v>1.075984412119574</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.479837801150577</v>
+        <v>9.51525636147082</v>
       </c>
       <c r="E8" t="n">
-        <v>375.3690634229048</v>
+        <v>372.9343262044087</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3608325729481372</v>
+        <v>-0.3586032788199399</v>
       </c>
       <c r="G8" t="n">
-        <v>1.172133282169166</v>
+        <v>1.172156537339553</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3078426134956047</v>
+        <v>-0.3059346319339419</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7394827202188133</v>
+        <v>0.7394901694037779</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731928769147207</v>
+        <v>1.73199460647133</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.326688739167762</v>
+        <v>7.34340306754351</v>
       </c>
       <c r="E9" t="n">
-        <v>224.1328936004049</v>
+        <v>226.0875431476167</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4154299044041103</v>
+        <v>0.420391461215718</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4815737349028132</v>
+        <v>0.4815500866414892</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8626506686207638</v>
+        <v>0.8729963359526849</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,45 +922,45 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788432051866262</v>
+        <v>0.6788415821602135</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532166804400541</v>
+        <v>0.653188332472198</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.577026347170241</v>
+        <v>6.595526500360436</v>
       </c>
       <c r="E10" t="n">
-        <v>379.1625186855754</v>
+        <v>257.4479739135309</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9415703216209741</v>
+        <v>-0.2821516786278344</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8243487678450718</v>
+        <v>0.9616124671348084</v>
       </c>
       <c r="H10" t="n">
-        <v>1.142198979786591</v>
+        <v>-0.2934151628342809</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3268819295856837</v>
+        <v>0.6126386245816655</v>
       </c>
       <c r="J10" t="n">
         <v>268</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6643207658256226</v>
+        <v>0.7135664691732531</v>
       </c>
       <c r="N10" t="n">
-        <v>1.09424310772979</v>
+        <v>1.371080757157208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.55643037871898</v>
+        <v>6.591744584446602</v>
       </c>
       <c r="E11" t="n">
-        <v>255.5841845867208</v>
+        <v>378.6292379065949</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2876726802723312</v>
+        <v>0.9448195729682807</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9616418261128674</v>
+        <v>0.8243465238751077</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2991474293866324</v>
+        <v>1.146143697588304</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6126386245816655</v>
+        <v>0.3268819295856837</v>
       </c>
       <c r="J11" t="n">
         <v>268</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7135707956237323</v>
+        <v>0.6643185637325029</v>
       </c>
       <c r="N11" t="n">
-        <v>1.37111982499502</v>
+        <v>1.094245365076432</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.264960691054393</v>
+        <v>6.291017527767471</v>
       </c>
       <c r="E12" t="n">
-        <v>96.88481891718564</v>
+        <v>97.81153064841554</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2834320662201184</v>
+        <v>-0.2804176958715542</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6606946023696949</v>
+        <v>0.660716016174442</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4289910424627967</v>
+        <v>-0.4244148605556406</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.789048258155477</v>
+        <v>0.7890320025958211</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041667999827576</v>
+        <v>1.041688738276151</v>
       </c>
     </row>
     <row r="13">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.624849210071578</v>
+        <v>4.636667567069956</v>
       </c>
       <c r="E13" t="n">
-        <v>201.1243772139795</v>
+        <v>201.9784212848139</v>
       </c>
       <c r="F13" t="n">
         <v>1.691286444456555</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6039937058097022</v>
+        <v>0.603997407869165</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042394688827745</v>
+        <v>1.042409521308802</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.572459419509251</v>
+        <v>4.600100580500889</v>
       </c>
       <c r="E14" t="n">
-        <v>136.5142322589455</v>
+        <v>143.7185380448759</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4036963333907216</v>
+        <v>-0.3975307347136803</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8534472473943604</v>
+        <v>0.8533720099483474</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4730184960151168</v>
+        <v>-0.4658352161535529</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601985263040427</v>
+        <v>0.7602182170041234</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296369199048927</v>
+        <v>1.296298990330339</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.018815210231915</v>
+        <v>4.024275352632982</v>
       </c>
       <c r="E15" t="n">
-        <v>241.0638716002964</v>
+        <v>241.5591523773441</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06783995715718083</v>
+        <v>-0.06681899947982073</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7939882508939553</v>
+        <v>0.7940009277827794</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0854420164036426</v>
+        <v>-0.08415481284941381</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7170393535387894</v>
+        <v>0.7170704630722932</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137580309942735</v>
+        <v>1.137657043420411</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.890220460043761</v>
+        <v>3.92420200503792</v>
       </c>
       <c r="E16" t="n">
-        <v>191.0847108094377</v>
+        <v>190.4138972829984</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4014511187557093</v>
+        <v>0.420223262108633</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9605428080168004</v>
+        <v>0.9603656576195869</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4179419338785864</v>
+        <v>0.4375658987538357</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.515822438474443</v>
+        <v>0.5158429916296747</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9900154070565159</v>
+        <v>0.9898802792494417</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.344093483246729</v>
+        <v>3.370043901918838</v>
       </c>
       <c r="E17" t="n">
-        <v>58.21168593919104</v>
+        <v>58.91616887583978</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2222632086124449</v>
+        <v>-0.2129134972140415</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559255421649097</v>
+        <v>0.7559791725625675</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2940279117648293</v>
+        <v>-0.2816393691010317</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244578560392059</v>
+        <v>0.7243910715240922</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094251485593087</v>
+        <v>1.094237100927482</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.082584293839066</v>
+        <v>3.083006900906895</v>
       </c>
       <c r="E18" t="n">
-        <v>60.07944859104794</v>
+        <v>61.48916735281445</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4784077226028313</v>
+        <v>-0.4774474100845573</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7485190763730568</v>
+        <v>0.7485026312607267</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6391389848351655</v>
+        <v>-0.6378700490075465</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645363005994433</v>
+        <v>0.7645222075230319</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143473178921461</v>
+        <v>1.143436240472864</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.980531528258254</v>
+        <v>2.98414083165591</v>
       </c>
       <c r="E19" t="n">
-        <v>75.98964820029538</v>
+        <v>74.39393514635358</v>
       </c>
       <c r="F19" t="n">
-        <v>0.122994109176451</v>
+        <v>0.122055324032732</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4829790733892665</v>
+        <v>0.4829807026259032</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2546572221304534</v>
+        <v>0.2527126308962928</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177239878892615</v>
+        <v>0.717724606785781</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926451124565257</v>
+        <v>0.6926536566041405</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.566973878863285</v>
+        <v>2.574062457749335</v>
       </c>
       <c r="E20" t="n">
-        <v>100.1233473686129</v>
+        <v>99.51820338643473</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3311138295212681</v>
+        <v>-0.3285890665299265</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7810850044290423</v>
+        <v>0.7810849539311421</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4239152302806092</v>
+        <v>-0.4206828781890655</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328430102929906</v>
+        <v>0.7328377451088356</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14375827365936</v>
+        <v>1.143759246513113</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.8405613573444</v>
+        <v>567.6570463794008</v>
       </c>
       <c r="E2" t="n">
-        <v>10626.78926035213</v>
+        <v>10795.34407686225</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6246520446385311</v>
+        <v>0.6208981335493471</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004624339627352</v>
+        <v>0.5004687617727961</v>
       </c>
       <c r="H2" t="n">
-        <v>1.248149715638883</v>
+        <v>1.240633144314457</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.3482538661895</v>
+        <v>222.6534332496921</v>
       </c>
       <c r="E3" t="n">
-        <v>4257.149412857553</v>
+        <v>4354.033657226427</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2550715341211798</v>
+        <v>0.2506581219536566</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999360964357482</v>
+        <v>0.5999484485950255</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4251645060808528</v>
+        <v>0.4177994335024186</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907285728537627</v>
+        <v>0.8907312410488819</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067772897059166</v>
+        <v>1.067784579180195</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.15924095207325</v>
+        <v>36.86064321739376</v>
       </c>
       <c r="E4" t="n">
-        <v>1733.487929051063</v>
+        <v>1727.534859425578</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7614478379672653</v>
+        <v>0.7474773329245405</v>
       </c>
       <c r="G4" t="n">
-        <v>1.112686358490045</v>
+        <v>1.11278251252558</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6843328599809355</v>
+        <v>0.6717191585155845</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735424062968398</v>
+        <v>0.4735712960113807</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052834618336764</v>
+        <v>1.052976522987822</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.67376664137493</v>
+        <v>36.5728870649033</v>
       </c>
       <c r="E5" t="n">
-        <v>358.9755300470716</v>
+        <v>355.8469272347152</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3469521588965258</v>
+        <v>-0.3491914700321407</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634103703765341</v>
+        <v>0.5634009021169566</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6158071933689353</v>
+        <v>-0.619792174134027</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366294062709446</v>
+        <v>0.7366364240272444</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292823166189179</v>
+        <v>0.8292657954495286</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.23792335730281</v>
+        <v>11.34556833927342</v>
       </c>
       <c r="E6" t="n">
-        <v>1364.440322426925</v>
+        <v>1347.749686126016</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4677592594370329</v>
+        <v>-0.4577473552520113</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8158611059843303</v>
+        <v>0.8154821771538496</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5733319752664087</v>
+        <v>-0.5613211031167051</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6695167882144167</v>
+        <v>0.669853785724605</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09145596200406</v>
+        <v>1.091484354832597</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.60445276429337</v>
+        <v>10.55702000337833</v>
       </c>
       <c r="E7" t="n">
-        <v>195.3126156050431</v>
+        <v>198.2055120719286</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3290780280359775</v>
+        <v>-0.3317951752568657</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169115907118367</v>
+        <v>0.7169396482540431</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4590217710237171</v>
+        <v>-0.4627937317525731</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511243851709059</v>
+        <v>0.7511330289361366</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075984412119574</v>
+        <v>1.076025300060476</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.51525636147082</v>
+        <v>9.471554558642854</v>
       </c>
       <c r="E8" t="n">
-        <v>372.9343262044087</v>
+        <v>374.7583960242848</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3586032788199399</v>
+        <v>-0.3600897041184938</v>
       </c>
       <c r="G8" t="n">
-        <v>1.172156537339553</v>
+        <v>1.172140187388816</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3059346319339419</v>
+        <v>-0.3072070286410603</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7394901694037779</v>
+        <v>0.739464305827412</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73199460647133</v>
+        <v>1.731887974245583</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.34340306754351</v>
+        <v>7.326793927307213</v>
       </c>
       <c r="E9" t="n">
-        <v>226.0875431476167</v>
+        <v>226.2231628899183</v>
       </c>
       <c r="F9" t="n">
-        <v>0.420391461215718</v>
+        <v>0.4166108089021319</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4815500866414892</v>
+        <v>0.4815664410458629</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8729963359526849</v>
+        <v>0.8651159495195287</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,45 +922,45 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788415821602135</v>
+        <v>0.6788534733019044</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653188332472198</v>
+        <v>0.6532136990360919</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.595526500360436</v>
+        <v>6.579828008536579</v>
       </c>
       <c r="E10" t="n">
-        <v>257.4479739135309</v>
+        <v>378.8073924899043</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2821516786278344</v>
+        <v>0.9460014768172527</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9616124671348084</v>
+        <v>0.8243463188528887</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2934151628342809</v>
+        <v>1.147577729386421</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6126386245816655</v>
+        <v>0.3268819295856837</v>
       </c>
       <c r="J10" t="n">
         <v>268</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7135664691732531</v>
+        <v>0.6643098655757663</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371080757157208</v>
+        <v>1.09421693039385</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.591744584446602</v>
+        <v>6.575334781185236</v>
       </c>
       <c r="E11" t="n">
-        <v>378.6292379065949</v>
+        <v>258.7236628530425</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9448195729682807</v>
+        <v>-0.2847755668375651</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8243465238751077</v>
+        <v>0.9616208532198175</v>
       </c>
       <c r="H11" t="n">
-        <v>1.146143697588304</v>
+        <v>-0.2961412139556296</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3268819295856837</v>
+        <v>0.6126386245816655</v>
       </c>
       <c r="J11" t="n">
         <v>268</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643185637325029</v>
+        <v>0.7135722265003311</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094245365076432</v>
+        <v>1.371086440741189</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.291017527767471</v>
+        <v>6.277005560604302</v>
       </c>
       <c r="E12" t="n">
-        <v>97.81153064841554</v>
+        <v>96.87096003287257</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2804176958715542</v>
+        <v>-0.2809831464111764</v>
       </c>
       <c r="G12" t="n">
-        <v>0.660716016174442</v>
+        <v>0.6607105207701935</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4244148605556406</v>
+        <v>-0.4252742125002534</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890320025958211</v>
+        <v>0.788999675087194</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041688738276151</v>
+        <v>1.041624225191971</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.636667567069956</v>
+        <v>4.614350971655696</v>
       </c>
       <c r="E13" t="n">
-        <v>201.9784212848139</v>
+        <v>196.4166602877155</v>
       </c>
       <c r="F13" t="n">
-        <v>1.691286444456555</v>
+        <v>1.677429470850134</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8637235846103802</v>
+        <v>0.8637365535153166</v>
       </c>
       <c r="H13" t="n">
-        <v>1.958133915284347</v>
+        <v>1.942061458465748</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.603997407869165</v>
+        <v>0.6040086684942915</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042409521308802</v>
+        <v>1.042431427229576</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.600100580500889</v>
+        <v>4.580415978946814</v>
       </c>
       <c r="E14" t="n">
-        <v>143.7185380448759</v>
+        <v>144.4391241362883</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3975307347136803</v>
+        <v>-0.4012321168273499</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8533720099483474</v>
+        <v>0.8534065232920333</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4658352161535529</v>
+        <v>-0.4701535620791704</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602182170041234</v>
+        <v>0.7602235343716881</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296298990330339</v>
+        <v>1.296344093674838</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.024275352632982</v>
+        <v>3.996865662016402</v>
       </c>
       <c r="E15" t="n">
-        <v>241.5591523773441</v>
+        <v>234.0523736400496</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06681899947982073</v>
+        <v>-0.07294028624838622</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7940009277827794</v>
+        <v>0.7939415840796668</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08415481284941381</v>
+        <v>-0.09187109947508071</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7170704630722932</v>
+        <v>0.7170964714800178</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137657043420411</v>
+        <v>1.137598891263571</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.92420200503792</v>
+        <v>3.872210678119731</v>
       </c>
       <c r="E16" t="n">
-        <v>190.4138972829984</v>
+        <v>188.6194186122808</v>
       </c>
       <c r="F16" t="n">
-        <v>0.420223262108633</v>
+        <v>0.3894184483754786</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9603656576195869</v>
+        <v>0.9607255998670132</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4375658987538357</v>
+        <v>0.4053378492562113</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158429916296747</v>
+        <v>0.5157817098886019</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9898802792494417</v>
+        <v>0.9901211234001457</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.370043901918838</v>
+        <v>3.357359341568007</v>
       </c>
       <c r="E17" t="n">
-        <v>58.91616887583978</v>
+        <v>58.53211419789664</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2129134972140415</v>
+        <v>-0.2165835888628074</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559791725625675</v>
+        <v>0.7559417212565501</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2816393691010317</v>
+        <v>-0.2865083150891518</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7243910715240922</v>
+        <v>0.7243979919907383</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094237100927482</v>
+        <v>1.094179510826031</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.083006900906895</v>
+        <v>3.076349657033744</v>
       </c>
       <c r="E18" t="n">
-        <v>61.48916735281445</v>
+        <v>61.3907194245404</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4774474100845573</v>
+        <v>-0.479047670064928</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7485026312607267</v>
+        <v>0.7485318298432432</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6378700490075465</v>
+        <v>-0.6399830320712611</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645222075230319</v>
+        <v>0.7645382135136596</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143436240472864</v>
+        <v>1.143490326787407</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.98414083165591</v>
+        <v>2.979233968637968</v>
       </c>
       <c r="E19" t="n">
-        <v>74.39393514635358</v>
+        <v>72.50677821740484</v>
       </c>
       <c r="F19" t="n">
-        <v>0.122055324032732</v>
+        <v>0.1211167475784629</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4829807026259032</v>
+        <v>0.4829833799355701</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2527126308962928</v>
+        <v>0.250767940699367</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.717724606785781</v>
+        <v>0.7177310932044318</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926536566041405</v>
+        <v>0.69265499819168</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.574062457749335</v>
+        <v>2.567042805461356</v>
       </c>
       <c r="E20" t="n">
-        <v>99.51820338643473</v>
+        <v>99.00997133476201</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3285890665299265</v>
+        <v>-0.3311138295212681</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7810849539311421</v>
+        <v>0.7810850044290423</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4206828781890655</v>
+        <v>-0.4239152302806092</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328377451088356</v>
+        <v>0.7328416804012946</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143759246513113</v>
+        <v>1.143751000870453</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.6570463794008</v>
+        <v>567.818204493641</v>
       </c>
       <c r="E2" t="n">
-        <v>10795.34407686225</v>
+        <v>10741.50088665058</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6208981335493471</v>
+        <v>0.6212011728045812</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004687617727961</v>
+        <v>0.5004679632556416</v>
       </c>
       <c r="H2" t="n">
-        <v>1.240633144314457</v>
+        <v>1.24124063559143</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.6534332496921</v>
+        <v>223.0648836759327</v>
       </c>
       <c r="E3" t="n">
-        <v>4354.033657226427</v>
+        <v>4373.531430992531</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2506581219536566</v>
+        <v>0.2515772420492248</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999484485950255</v>
+        <v>0.5999446424932047</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4177994335024186</v>
+        <v>0.4193340922318085</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907312410488819</v>
+        <v>0.8907311524482171</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067784579180195</v>
+        <v>1.067779402575139</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.86064321739376</v>
+        <v>36.88440058815731</v>
       </c>
       <c r="E4" t="n">
-        <v>1727.534859425578</v>
+        <v>1659.22449593407</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7474773329245405</v>
+        <v>0.7546292642359664</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11278251252558</v>
+        <v>1.112728219332986</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6717191585155845</v>
+        <v>0.6781793173973079</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735712960113807</v>
+        <v>0.4735746389994725</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052976522987822</v>
+        <v>1.052934260461285</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.5728870649033</v>
+        <v>36.58526391841106</v>
       </c>
       <c r="E5" t="n">
-        <v>355.8469272347152</v>
+        <v>355.6647198519673</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3491914700321407</v>
+        <v>-0.3484452601326762</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634009021169566</v>
+        <v>0.5634023703083325</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.619792174134027</v>
+        <v>-0.6184660883517104</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366364240272444</v>
+        <v>0.7366274657637307</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292657954495286</v>
+        <v>0.8292591948258488</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.34556833927342</v>
+        <v>11.27752805939343</v>
       </c>
       <c r="E6" t="n">
-        <v>1347.749686126016</v>
+        <v>1326.598329653512</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4577473552520113</v>
+        <v>-0.4655790764863371</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8154821771538496</v>
+        <v>0.8157530800488174</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5613211031167051</v>
+        <v>-0.5707352970809197</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.669853785724605</v>
+        <v>0.6697003037922956</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091484354832597</v>
+        <v>1.09159851506646</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.55702000337833</v>
+        <v>10.57348668159569</v>
       </c>
       <c r="E7" t="n">
-        <v>198.2055120719286</v>
+        <v>194.235076710856</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3317951752568657</v>
+        <v>-0.3290780280359775</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169396482540431</v>
+        <v>0.7169115907118367</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4627937317525731</v>
+        <v>-0.4590217710237171</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511330289361366</v>
+        <v>0.7511369694239427</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076025300060476</v>
+        <v>1.075990551101708</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.471554558642854</v>
+        <v>9.528122793050644</v>
       </c>
       <c r="E8" t="n">
-        <v>374.7583960242848</v>
+        <v>371.2234512642656</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3600897041184938</v>
+        <v>-0.3545108889948142</v>
       </c>
       <c r="G8" t="n">
-        <v>1.172140187388816</v>
+        <v>1.172218957689692</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3072070286410603</v>
+        <v>-0.302427193033556</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.739464305827412</v>
+        <v>0.7393871385284478</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731887974245583</v>
+        <v>1.731826379488458</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.326793927307213</v>
+        <v>7.33158115242642</v>
       </c>
       <c r="E9" t="n">
-        <v>226.2231628899183</v>
+        <v>222.3810968479704</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4166108089021319</v>
+        <v>0.4182645147822706</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4815664410458629</v>
+        <v>0.4815579760924851</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8651159495195287</v>
+        <v>0.8685652310780981</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788534733019044</v>
+        <v>0.6788534440959102</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532136990360919</v>
+        <v>0.6532032309833459</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.579828008536579</v>
+        <v>6.585960464455427</v>
       </c>
       <c r="E10" t="n">
-        <v>378.8073924899043</v>
+        <v>373.7174073686962</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9460014768172527</v>
+        <v>0.9451150310403937</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8243463188528887</v>
+        <v>0.8243464420711555</v>
       </c>
       <c r="H10" t="n">
-        <v>1.147577729386421</v>
+        <v>1.146502226255516</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6643098655757663</v>
+        <v>0.6643130935107855</v>
       </c>
       <c r="N10" t="n">
-        <v>1.09421693039385</v>
+        <v>1.09422415671624</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.575334781185236</v>
+        <v>6.583036011355088</v>
       </c>
       <c r="E11" t="n">
-        <v>258.7236628530425</v>
+        <v>257.5940194816981</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2847755668375651</v>
+        <v>-0.2836710830428067</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9616208532198175</v>
+        <v>0.9616160960722367</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2961412139556296</v>
+        <v>-0.2949941085652307</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7135722265003311</v>
+        <v>0.7135689017577616</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371086440741189</v>
+        <v>1.371075457304243</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.277005560604302</v>
+        <v>6.282059114564133</v>
       </c>
       <c r="E12" t="n">
-        <v>96.87096003287257</v>
+        <v>95.60283382768918</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2809831464111764</v>
+        <v>-0.2802291861100341</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6607105207701935</v>
+        <v>0.6607179997968595</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4252742125002534</v>
+        <v>-0.4241282759001446</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.788999675087194</v>
+        <v>0.7889878462479675</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041624225191971</v>
+        <v>1.041622061571816</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.614350971655696</v>
+        <v>4.600066445222461</v>
       </c>
       <c r="E13" t="n">
-        <v>196.4166602877155</v>
+        <v>189.5560116183633</v>
       </c>
       <c r="F13" t="n">
-        <v>1.677429470850134</v>
+        <v>1.663591530010339</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8637365535153166</v>
+        <v>0.8637719298678886</v>
       </c>
       <c r="H13" t="n">
-        <v>1.942061458465748</v>
+        <v>1.925961555922268</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040086684942915</v>
+        <v>0.6040079177378921</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042431427229576</v>
+        <v>1.042474490007353</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.580415978946814</v>
+        <v>4.584933978039579</v>
       </c>
       <c r="E14" t="n">
-        <v>144.4391241362883</v>
+        <v>142.1687956691707</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4012321168273499</v>
+        <v>-0.4018484241161812</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8534065232920333</v>
+        <v>0.8534153757663578</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4701535620791704</v>
+        <v>-0.4708708508507075</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602235343716881</v>
+        <v>0.7602187431000595</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296344093674838</v>
+        <v>1.296351438935092</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.996865662016402</v>
+        <v>4.036865540681187</v>
       </c>
       <c r="E15" t="n">
-        <v>234.0523736400496</v>
+        <v>224.2771508501523</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07294028624838622</v>
+        <v>-0.0574464038847412</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7939415840796668</v>
+        <v>0.7941690518802313</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09187109947508071</v>
+        <v>-0.07233523359885938</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7170964714800178</v>
+        <v>0.7168070638616347</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137598891263571</v>
+        <v>1.137467386693168</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.872210678119731</v>
+        <v>3.830374505136033</v>
       </c>
       <c r="E16" t="n">
-        <v>188.6194186122808</v>
+        <v>190.8341304431738</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3894184483754786</v>
+        <v>0.3774134076155089</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9607255998670132</v>
+        <v>0.960962285874311</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4053378492562113</v>
+        <v>0.3927452858070568</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5157817098886019</v>
+        <v>0.5156826704181391</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9901211234001457</v>
+        <v>0.9901764630989047</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.357359341568007</v>
+        <v>3.362267575719581</v>
       </c>
       <c r="E17" t="n">
-        <v>58.53211419789664</v>
+        <v>56.62132447249465</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2165835888628074</v>
+        <v>-0.2149326117590783</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559417212565501</v>
+        <v>0.7559559526591839</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2865083150891518</v>
+        <v>-0.2843189619752605</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7243979919907383</v>
+        <v>0.7243760572857354</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094179510826031</v>
+        <v>1.094168723421816</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.076349657033744</v>
+        <v>3.078434847176419</v>
       </c>
       <c r="E18" t="n">
-        <v>61.3907194245404</v>
+        <v>60.88724760537035</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.479047670064928</v>
+        <v>-0.4776875322202846</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7485318298432432</v>
+        <v>0.7485064404560283</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6399830320712611</v>
+        <v>-0.6381876045438607</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645382135136596</v>
+        <v>0.764546938416889</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143490326787407</v>
+        <v>1.143466414340017</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.979233968637968</v>
+        <v>2.984773776793896</v>
       </c>
       <c r="E19" t="n">
-        <v>72.50677821740484</v>
+        <v>73.46502101799665</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1211167475784629</v>
+        <v>0.125811715927217</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4829833799355701</v>
+        <v>0.4829804741894875</v>
       </c>
       <c r="H19" t="n">
-        <v>0.250767940699367</v>
+        <v>0.2604902737286586</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177310932044318</v>
+        <v>0.7176993079695957</v>
       </c>
       <c r="N19" t="n">
-        <v>0.69265499819168</v>
+        <v>0.6926212615762575</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.567042805461356</v>
+        <v>2.568927221357504</v>
       </c>
       <c r="E20" t="n">
-        <v>99.00997133476201</v>
+        <v>96.86798395559738</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3311138295212681</v>
+        <v>-0.3290942213196093</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7810850044290423</v>
+        <v>0.7810839118196563</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4239152302806092</v>
+        <v>-0.4213301750805918</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328416804012946</v>
+        <v>0.7328272533728263</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143751000870453</v>
+        <v>1.143728709484081</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.818204493641</v>
+        <v>567.7170095135327</v>
       </c>
       <c r="E2" t="n">
-        <v>10741.50088665058</v>
+        <v>10669.20680138313</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6212011728045812</v>
+        <v>0.61960906251685</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004679632556416</v>
+        <v>0.5004727235867558</v>
       </c>
       <c r="H2" t="n">
-        <v>1.24124063559143</v>
+        <v>1.238047616414089</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.0648836759327</v>
+        <v>223.1009161771146</v>
       </c>
       <c r="E3" t="n">
-        <v>4373.531430992531</v>
+        <v>4349.949755130247</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2515772420492248</v>
+        <v>0.2505754099473041</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999446424932047</v>
+        <v>0.5999488229673933</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4193340922318085</v>
+        <v>0.4176613076894438</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907311524482171</v>
+        <v>0.8907331940475576</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067779402575139</v>
+        <v>1.067779133929529</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.88440058815731</v>
+        <v>37.00557647398151</v>
       </c>
       <c r="E4" t="n">
-        <v>1659.22449593407</v>
+        <v>1626.245440313579</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7546292642359664</v>
+        <v>0.7522444246742579</v>
       </c>
       <c r="G4" t="n">
-        <v>1.112728219332986</v>
+        <v>1.112745140300099</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6781793173973079</v>
+        <v>0.6760258009047637</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735746389994725</v>
+        <v>0.4735934752040847</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052934260461285</v>
+        <v>1.052982137037141</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.58526391841106</v>
+        <v>36.53912960765117</v>
       </c>
       <c r="E5" t="n">
-        <v>355.6647198519673</v>
+        <v>351.5779403983935</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3484452601326762</v>
+        <v>-0.3506832077838461</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634023703083325</v>
+        <v>0.5634030294856331</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6184660883517104</v>
+        <v>-0.6224375614451476</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366274657637307</v>
+        <v>0.7366495594956849</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292591948258488</v>
+        <v>0.8292771492414438</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.27752805939343</v>
+        <v>11.21218461473297</v>
       </c>
       <c r="E6" t="n">
-        <v>1326.598329653512</v>
+        <v>1292.196950126627</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4655790764863371</v>
+        <v>-0.4751903024950582</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8157530800488174</v>
+        <v>0.8163368394727449</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5707352970809197</v>
+        <v>-0.5821007695817989</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6697003037922956</v>
+        <v>0.6693847022383992</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09159851506646</v>
+        <v>1.091854493688455</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.57348668159569</v>
+        <v>10.57038036572582</v>
       </c>
       <c r="E7" t="n">
-        <v>194.235076710856</v>
+        <v>193.8344910808499</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3290780280359775</v>
+        <v>-0.3323985876244604</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169115907118367</v>
+        <v>0.7169481176317858</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4590217710237171</v>
+        <v>-0.4636299049398935</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511369694239427</v>
+        <v>0.7511394431005927</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075990551101708</v>
+        <v>1.076038681889534</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.528122793050644</v>
+        <v>9.525578323284101</v>
       </c>
       <c r="E8" t="n">
-        <v>371.2234512642656</v>
+        <v>370.6352789161804</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3545108889948142</v>
+        <v>-0.3578597226000904</v>
       </c>
       <c r="G8" t="n">
-        <v>1.172218957689692</v>
+        <v>1.172165982035217</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.302427193033556</v>
+        <v>-0.3052978230768504</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7393871385284478</v>
+        <v>0.739415581614407</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731826379488458</v>
+        <v>1.731798258941377</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.33158115242642</v>
+        <v>7.343920514564613</v>
       </c>
       <c r="E9" t="n">
-        <v>222.3810968479704</v>
+        <v>218.6052904829554</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4182645147822706</v>
+        <v>0.4206278408768001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4815579760924851</v>
+        <v>0.4815494179635826</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8685652310780981</v>
+        <v>0.8734884213038552</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788534440959102</v>
+        <v>0.6788524033501716</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532032309833459</v>
+        <v>0.6531844080805074</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.585960464455427</v>
+        <v>6.57539946453811</v>
       </c>
       <c r="E10" t="n">
-        <v>373.7174073686962</v>
+        <v>369.180153648419</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9451150310403937</v>
+        <v>0.9371418523663821</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8243464420711555</v>
+        <v>0.8243557990511202</v>
       </c>
       <c r="H10" t="n">
-        <v>1.146502226255516</v>
+        <v>1.136817201316574</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6643130935107855</v>
+        <v>0.6643278792197364</v>
       </c>
       <c r="N10" t="n">
-        <v>1.09422415671624</v>
+        <v>1.094250523347831</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.583036011355088</v>
+        <v>6.571481751723472</v>
       </c>
       <c r="E11" t="n">
-        <v>257.5940194816981</v>
+        <v>255.0083276776436</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2836710830428067</v>
+        <v>-0.2883620083705022</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9616160960722367</v>
+        <v>0.9616486309254144</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2949941085652307</v>
+        <v>-0.2998621316530191</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7135689017577616</v>
+        <v>0.7135807082719924</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371075457304243</v>
+        <v>1.371131489937424</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.282059114564133</v>
+        <v>6.271336207362502</v>
       </c>
       <c r="E12" t="n">
-        <v>95.60283382768918</v>
+        <v>94.42050830880912</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2802291861100341</v>
+        <v>-0.2843733669470893</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6607179997968595</v>
+        <v>0.660691896150319</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4241282759001446</v>
+        <v>-0.4304175192764728</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7889878462479675</v>
+        <v>0.7890451604701201</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041622061571816</v>
+        <v>1.041646664543682</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.600066445222461</v>
+        <v>4.597923473221766</v>
       </c>
       <c r="E13" t="n">
-        <v>189.5560116183633</v>
+        <v>185.5046810762526</v>
       </c>
       <c r="F13" t="n">
-        <v>1.663591530010339</v>
+        <v>1.657447455453443</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8637719298678886</v>
+        <v>0.8637948445486034</v>
       </c>
       <c r="H13" t="n">
-        <v>1.925961555922268</v>
+        <v>1.918797577820207</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040079177378921</v>
+        <v>0.6040186107638214</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042474490007353</v>
+        <v>1.042510685197721</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.584933978039579</v>
+        <v>4.56643977950251</v>
       </c>
       <c r="E14" t="n">
-        <v>142.1687956691707</v>
+        <v>140.8936270166831</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4018484241161812</v>
+        <v>-0.4055427220630972</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8534153757663578</v>
+        <v>0.8534870896063864</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4708708508507075</v>
+        <v>-0.4751597616434087</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602187431000595</v>
+        <v>0.7602054095321241</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296351438935092</v>
+        <v>1.296425303330505</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.036865540681187</v>
+        <v>4.034732349925882</v>
       </c>
       <c r="E15" t="n">
-        <v>224.2771508501523</v>
+        <v>221.2463590185395</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0574464038847412</v>
+        <v>-0.06358400864288127</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7941690518802313</v>
+        <v>0.7940484228926596</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.07233523359885938</v>
+        <v>-0.08007573191978574</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7168070638616347</v>
+        <v>0.7169139623334321</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137467386693168</v>
+        <v>1.137453400178978</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.830374505136033</v>
+        <v>3.850456414378486</v>
       </c>
       <c r="E16" t="n">
-        <v>190.8341304431738</v>
+        <v>189.9602296234384</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3774134076155089</v>
+        <v>0.3800788009601661</v>
       </c>
       <c r="G16" t="n">
-        <v>0.960962285874311</v>
+        <v>0.9609050333616546</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3927452858070568</v>
+        <v>0.395542522688729</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5156826704181391</v>
+        <v>0.515758752043768</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9901764630989047</v>
+        <v>0.990254128711316</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.362267575719581</v>
+        <v>3.359718809820967</v>
       </c>
       <c r="E17" t="n">
-        <v>56.62132447249465</v>
+        <v>55.68952858340919</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2149326117590783</v>
+        <v>-0.2184169239903895</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559559526591839</v>
+        <v>0.7559309404221597</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2843189619752605</v>
+        <v>-0.2889376691849809</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7243760572857354</v>
+        <v>0.7244108092513104</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094168723421816</v>
+        <v>1.094174604291686</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.078434847176419</v>
+        <v>3.072443260365961</v>
       </c>
       <c r="E18" t="n">
-        <v>60.88724760537035</v>
+        <v>60.34378323186679</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4776875322202846</v>
+        <v>-0.4812858407239987</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7485064404560283</v>
+        <v>0.7485877431617858</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6381876045438607</v>
+        <v>-0.6429250881015061</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764546938416889</v>
+        <v>0.7645242627162939</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143466414340017</v>
+        <v>1.143545822672611</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.984773776793896</v>
+        <v>2.974911470249695</v>
       </c>
       <c r="E19" t="n">
-        <v>73.46502101799665</v>
+        <v>74.15518271233988</v>
       </c>
       <c r="F19" t="n">
-        <v>0.125811715927217</v>
+        <v>0.1173645302937756</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4829804741894875</v>
+        <v>0.4830045694536318</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2604902737286586</v>
+        <v>0.2429884471414768</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7176993079695957</v>
+        <v>0.7177384960002959</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926212615762575</v>
+        <v>0.6926870474706814</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.568927221357504</v>
+        <v>2.566637380245544</v>
       </c>
       <c r="E20" t="n">
-        <v>96.86798395559738</v>
+        <v>95.38735258012859</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3290942213196093</v>
+        <v>-0.3321230265478015</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7810839118196563</v>
+        <v>0.781088707355485</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4213301750805918</v>
+        <v>-0.4252052595565786</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328272533728263</v>
+        <v>0.7328459218069954</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143728709484081</v>
+        <v>1.143753988534277</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.7170095135327</v>
+        <v>567.1078619586991</v>
       </c>
       <c r="E2" t="n">
-        <v>10669.20680138313</v>
+        <v>10445.76687215887</v>
       </c>
       <c r="F2" t="n">
-        <v>0.61960906251685</v>
+        <v>0.6179123776724305</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004727235867558</v>
+        <v>0.5004793336770595</v>
       </c>
       <c r="H2" t="n">
-        <v>1.238047616414089</v>
+        <v>1.23464114518492</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.1009161771146</v>
+        <v>222.7891834249923</v>
       </c>
       <c r="E3" t="n">
-        <v>4349.949755130247</v>
+        <v>4320.299156879691</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2505754099473041</v>
+        <v>0.2486734351354918</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999488229673933</v>
+        <v>0.5999588839361539</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4176613076894438</v>
+        <v>0.4144841284856363</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907331940475576</v>
+        <v>0.8907363321359142</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067779133929529</v>
+        <v>1.067786699169636</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.00557647398151</v>
+        <v>36.72089391564442</v>
       </c>
       <c r="E4" t="n">
-        <v>1626.245440313579</v>
+        <v>1620.875102416124</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7522444246742579</v>
+        <v>0.7427136946786814</v>
       </c>
       <c r="G4" t="n">
-        <v>1.112745140300099</v>
+        <v>1.112824591404653</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6760258009047637</v>
+        <v>0.6674130859574171</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735934752040847</v>
+        <v>0.4736148231252364</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052982137037141</v>
+        <v>1.053090880207281</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.53912960765117</v>
+        <v>36.5365686557377</v>
       </c>
       <c r="E5" t="n">
-        <v>351.5779403983935</v>
+        <v>348.74698950573</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3506832077838461</v>
+        <v>-0.3495644897488727</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634030294856331</v>
+        <v>0.5634008009902121</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6224375614451476</v>
+        <v>-0.6204543712655205</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366495594956849</v>
+        <v>0.7366261849133902</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292771492414438</v>
+        <v>0.8292366031608449</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.21218461473297</v>
+        <v>11.05127745924453</v>
       </c>
       <c r="E6" t="n">
-        <v>1292.196950126627</v>
+        <v>1291.377734125593</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4751903024950582</v>
+        <v>-0.4777213607234894</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8163368394727449</v>
+        <v>0.816537038409377</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5821007695817989</v>
+        <v>-0.5850577968319671</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6693847022383992</v>
+        <v>0.6693376244359478</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091854493688455</v>
+        <v>1.09203102860898</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.57038036572582</v>
+        <v>10.5444847953019</v>
       </c>
       <c r="E7" t="n">
-        <v>193.8344910808499</v>
+        <v>192.2396790358843</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3323985876244604</v>
+        <v>-0.3333034344582969</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169481176317858</v>
+        <v>0.7169623450144657</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4636299049398935</v>
+        <v>-0.4648827609650436</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511394431005927</v>
+        <v>0.7511485822888736</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076038681889534</v>
+        <v>1.076058915470874</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.525578323284101</v>
+        <v>9.586228496022255</v>
       </c>
       <c r="E8" t="n">
-        <v>370.6352789161804</v>
+        <v>376.291596030428</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3578597226000904</v>
+        <v>-0.3526484273222116</v>
       </c>
       <c r="G8" t="n">
-        <v>1.172165982035217</v>
+        <v>1.172255794226866</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3052978230768504</v>
+        <v>-0.3008289053113981</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.739415581614407</v>
+        <v>0.7392820986155871</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731798258941377</v>
+        <v>1.731595423337742</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.343920514564613</v>
+        <v>7.252243131774019</v>
       </c>
       <c r="E9" t="n">
-        <v>218.6052904829554</v>
+        <v>226.8745478518507</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4206278408768001</v>
+        <v>0.3993956347977947</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4815494179635826</v>
+        <v>0.4817761021529238</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8734884213038552</v>
+        <v>0.8290067378041509</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788524033501716</v>
+        <v>0.6787519037680604</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531844080805074</v>
+        <v>0.6533865127331262</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.57539946453811</v>
+        <v>6.568783215343841</v>
       </c>
       <c r="E10" t="n">
-        <v>369.180153648419</v>
+        <v>364.8776757747267</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9371418523663821</v>
+        <v>0.9374370000297931</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8243557990511202</v>
+        <v>0.8243551877482279</v>
       </c>
       <c r="H10" t="n">
-        <v>1.136817201316574</v>
+        <v>1.137176078906538</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6643278792197364</v>
+        <v>0.6643268266758791</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094250523347831</v>
+        <v>1.094233525902092</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.571481751723472</v>
+        <v>6.558527400008598</v>
       </c>
       <c r="E11" t="n">
-        <v>255.0083276776436</v>
+        <v>254.4184042967558</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2883620083705022</v>
+        <v>-0.2882241569404999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9616486309254144</v>
+        <v>0.9616472142333754</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2998621316530191</v>
+        <v>-0.2997192241338441</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7135807082719924</v>
+        <v>0.7135864713936013</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371131489937424</v>
+        <v>1.371122434344255</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.271336207362502</v>
+        <v>6.258909094575758</v>
       </c>
       <c r="E12" t="n">
-        <v>94.42050830880912</v>
+        <v>93.84525022861312</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2843733669470893</v>
+        <v>-0.2856906353246973</v>
       </c>
       <c r="G12" t="n">
-        <v>0.660691896150319</v>
+        <v>0.6606912960150964</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4304175192764728</v>
+        <v>-0.4324116831080055</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890451604701201</v>
+        <v>0.789052386165552</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041646664543682</v>
+        <v>1.041641499578704</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.597923473221766</v>
+        <v>4.580769520213924</v>
       </c>
       <c r="E13" t="n">
-        <v>185.5046810762526</v>
+        <v>180.7631252699086</v>
       </c>
       <c r="F13" t="n">
-        <v>1.657447455453443</v>
+        <v>1.64977266819788</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8637948445486034</v>
+        <v>0.8638297109151446</v>
       </c>
       <c r="H13" t="n">
-        <v>1.918797577820207</v>
+        <v>1.909835523543297</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040186107638214</v>
+        <v>0.6040326383005822</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042510685197721</v>
+        <v>1.042563207341524</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.56643977950251</v>
+        <v>4.563047256110965</v>
       </c>
       <c r="E14" t="n">
-        <v>140.8936270166831</v>
+        <v>138.562785741196</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4055427220630972</v>
+        <v>-0.4049274282644054</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8534870896063864</v>
+        <v>0.8534729233129073</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4751597616434087</v>
+        <v>-0.4744467190506846</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602054095321241</v>
+        <v>0.7602294195171554</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296425303330505</v>
+        <v>1.296427607303462</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.034732349925882</v>
+        <v>4.031838148192944</v>
       </c>
       <c r="E15" t="n">
-        <v>221.2463590185395</v>
+        <v>221.1138773510844</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06358400864288127</v>
+        <v>-0.064094994426386</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7940484228926596</v>
+        <v>0.7940401808133861</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08007573191978574</v>
+        <v>-0.08072008945533386</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7169139623334321</v>
+        <v>0.7168851507191148</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137453400178978</v>
+        <v>1.137380859499673</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.850456414378486</v>
+        <v>3.859729135545103</v>
       </c>
       <c r="E16" t="n">
-        <v>189.9602296234384</v>
+        <v>187.7857816752799</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3800788009601661</v>
+        <v>0.3894184483754786</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9609050333616546</v>
+        <v>0.9607255998670132</v>
       </c>
       <c r="H16" t="n">
-        <v>0.395542522688729</v>
+        <v>0.4053378492562113</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.515758752043768</v>
+        <v>0.5158620442384912</v>
       </c>
       <c r="N16" t="n">
-        <v>0.990254128711316</v>
+        <v>0.9902544192153221</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.359718809820967</v>
+        <v>3.348463651218236</v>
       </c>
       <c r="E17" t="n">
-        <v>55.68952858340919</v>
+        <v>56.69490661490332</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2184169239903895</v>
+        <v>-0.2213478840332738</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559309404221597</v>
+        <v>0.7559247086605428</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2889376691849809</v>
+        <v>-0.2928173685782677</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244108092513104</v>
+        <v>0.7244351853252837</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094174604291686</v>
+        <v>1.094187950553457</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.072443260365961</v>
+        <v>3.067373508468339</v>
       </c>
       <c r="E18" t="n">
-        <v>60.34378323186679</v>
+        <v>60.03572521525144</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4812858407239987</v>
+        <v>-0.480966258889146</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7485877431617858</v>
+        <v>0.7485786817122153</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6429250881015061</v>
+        <v>-0.6425059524658617</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645242627162939</v>
+        <v>0.7645494337237174</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143545822672611</v>
+        <v>1.143554526009702</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.974911470249695</v>
+        <v>2.971979510802372</v>
       </c>
       <c r="E19" t="n">
-        <v>74.15518271233988</v>
+        <v>74.17152596412568</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1173645302937756</v>
+        <v>0.1164269985158952</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4830045694536318</v>
+        <v>0.4830124867305838</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2429884471414768</v>
+        <v>0.2410434548058304</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177384960002959</v>
+        <v>0.7177479863316012</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926870474706814</v>
+        <v>0.6926984120938674</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.566637380245544</v>
+        <v>2.556991429280946</v>
       </c>
       <c r="E20" t="n">
-        <v>95.38735258012859</v>
+        <v>94.33764450505423</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3321230265478015</v>
+        <v>-0.335148185891149</v>
       </c>
       <c r="G20" t="n">
-        <v>0.781088707355485</v>
+        <v>0.7811124422116438</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4252052595565786</v>
+        <v>-0.4290652251578654</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328459218069954</v>
+        <v>0.7328615022723222</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143753988534277</v>
+        <v>1.143797953927516</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.1078619586991</v>
+        <v>567.5511669077325</v>
       </c>
       <c r="E2" t="n">
-        <v>10445.76687215887</v>
+        <v>10441.43502783412</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6179123776724305</v>
+        <v>0.6197949258127819</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004793336770595</v>
+        <v>0.5004720958888229</v>
       </c>
       <c r="H2" t="n">
-        <v>1.23464114518492</v>
+        <v>1.238420545129585</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.7891834249923</v>
+        <v>222.910880996469</v>
       </c>
       <c r="E3" t="n">
-        <v>4320.299156879691</v>
+        <v>4340.272661670291</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2486734351354918</v>
+        <v>0.2498402560127657</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999588839361539</v>
+        <v>0.5999523816884058</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4144841284856363</v>
+        <v>0.4164334764530095</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907363321359142</v>
+        <v>0.8907329914729231</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067786699169636</v>
+        <v>1.06778656407116</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.72089391564442</v>
+        <v>36.80085687169376</v>
       </c>
       <c r="E4" t="n">
-        <v>1620.875102416124</v>
+        <v>1608.390010380342</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7427136946786814</v>
+        <v>0.7478177250008815</v>
       </c>
       <c r="G4" t="n">
-        <v>1.112824591404653</v>
+        <v>1.112779686986944</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6674130859574171</v>
+        <v>0.6720267576286696</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4736148231252364</v>
+        <v>0.4735884890138011</v>
       </c>
       <c r="N4" t="n">
-        <v>1.053090880207281</v>
+        <v>1.053005062409048</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.5365686557377</v>
+        <v>36.54720812834881</v>
       </c>
       <c r="E5" t="n">
-        <v>348.74698950573</v>
+        <v>348.2509795845411</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3495644897488727</v>
+        <v>-0.3491914700321407</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634008009902121</v>
+        <v>0.5634009021169566</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6204543712655205</v>
+        <v>-0.619792174134027</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366261849133902</v>
+        <v>0.7366307761297266</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292366031608449</v>
+        <v>0.8292539128710901</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.05127745924453</v>
+        <v>11.05606365607612</v>
       </c>
       <c r="E6" t="n">
-        <v>1291.377734125593</v>
+        <v>1274.335320696451</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4777213607234894</v>
+        <v>-0.4787148147310611</v>
       </c>
       <c r="G6" t="n">
-        <v>0.816537038409377</v>
+        <v>0.8166209412627525</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5850577968319671</v>
+        <v>-0.5862142280980667</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6693376244359478</v>
+        <v>0.6691861543252466</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09203102860898</v>
+        <v>1.091911880230941</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.5444847953019</v>
+        <v>10.54358632848094</v>
       </c>
       <c r="E7" t="n">
-        <v>192.2396790358843</v>
+        <v>190.8749450703483</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3333034344582969</v>
+        <v>-0.3327002394724179</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169623450144657</v>
+        <v>0.7169526569877281</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4648827609650436</v>
+        <v>-0.4640477111421216</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511485822888736</v>
+        <v>0.7511367362749174</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076058915470874</v>
+        <v>1.07604296674519</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.586228496022255</v>
+        <v>9.649253103893372</v>
       </c>
       <c r="E8" t="n">
-        <v>376.291596030428</v>
+        <v>390.0286317467279</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3526484273222116</v>
+        <v>-0.3440627778985386</v>
       </c>
       <c r="G8" t="n">
-        <v>1.172255794226866</v>
+        <v>1.172493356551668</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3008289053113981</v>
+        <v>-0.2934453964928516</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7392820986155871</v>
+        <v>0.7391123766885919</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731595423337742</v>
+        <v>1.731573765113567</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.252243131774019</v>
+        <v>7.287682569739591</v>
       </c>
       <c r="E9" t="n">
-        <v>226.8745478518507</v>
+        <v>225.5396392520842</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3993956347977947</v>
+        <v>0.4076425047657968</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4817761021529238</v>
+        <v>0.4816479420960339</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8290067378041509</v>
+        <v>0.8463495203401461</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,45 +922,45 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6787519037680604</v>
+        <v>0.6788159107329639</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6533865127331262</v>
+        <v>0.6532837477900213</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.568783215343841</v>
+        <v>6.574720341437972</v>
       </c>
       <c r="E10" t="n">
-        <v>364.8776757747267</v>
+        <v>256.0414595777519</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9374370000297931</v>
+        <v>-0.2844994883525452</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8243551877482279</v>
+        <v>0.9616194967301733</v>
       </c>
       <c r="H10" t="n">
-        <v>1.137176078906538</v>
+        <v>-0.2958545342725873</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3268819295856837</v>
+        <v>0.6126386245816655</v>
       </c>
       <c r="J10" t="n">
         <v>268</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6643268266758791</v>
+        <v>0.713571311209043</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094233525902092</v>
+        <v>1.371073613899069</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.558527400008598</v>
+        <v>6.564564052899226</v>
       </c>
       <c r="E11" t="n">
-        <v>254.4184042967558</v>
+        <v>361.9361741303366</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2882241569404999</v>
+        <v>0.9353712173719388</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9616472142333754</v>
+        <v>0.8243598945297255</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2997192241338441</v>
+        <v>1.134663662775034</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6126386245816655</v>
+        <v>0.3268819295856837</v>
       </c>
       <c r="J11" t="n">
         <v>268</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7135864713936013</v>
+        <v>0.6643304537366289</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371122434344255</v>
+        <v>1.09426157277082</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.258909094575758</v>
+        <v>6.266791276004766</v>
       </c>
       <c r="E12" t="n">
-        <v>93.84525022861312</v>
+        <v>93.38707204310833</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2856906353246973</v>
+        <v>-0.2828671279839802</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6606912960150964</v>
+        <v>0.6606971371122401</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4324116831080055</v>
+        <v>-0.42813433280539</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.789052386165552</v>
+        <v>0.7890230107284056</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041641499578704</v>
+        <v>1.041626992965744</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.580769520213924</v>
+        <v>4.585903690570255</v>
       </c>
       <c r="E13" t="n">
-        <v>180.7631252699086</v>
+        <v>180.2444459732875</v>
       </c>
       <c r="F13" t="n">
-        <v>1.64977266819788</v>
+        <v>1.654376832709282</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8638297109151446</v>
+        <v>0.8638079613972001</v>
       </c>
       <c r="H13" t="n">
-        <v>1.909835523543297</v>
+        <v>1.915213689433176</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040326383005822</v>
+        <v>0.6040148643475722</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042563207341524</v>
+        <v>1.042521357157917</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.563047256110965</v>
+        <v>4.570747698672552</v>
       </c>
       <c r="E14" t="n">
-        <v>138.562785741196</v>
+        <v>139.5817238978109</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4049274282644054</v>
+        <v>-0.403080532479396</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8534729233129073</v>
+        <v>0.8534357378492193</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4744467190506846</v>
+        <v>-0.4723033201014254</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602294195171554</v>
+        <v>0.7602230038329006</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296427607303462</v>
+        <v>1.296378930085663</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.031838148192944</v>
+        <v>4.032964108275764</v>
       </c>
       <c r="E15" t="n">
-        <v>221.1138773510844</v>
+        <v>220.2603192591197</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.064094994426386</v>
+        <v>-0.06341366357802913</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7940401808133861</v>
+        <v>0.7940512321525979</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08072008945533386</v>
+        <v>-0.07986092207944906</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7168851507191148</v>
+        <v>0.7169145466808555</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137380859499673</v>
+        <v>1.137459778110215</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.859729135545103</v>
+        <v>3.848124734556887</v>
       </c>
       <c r="E16" t="n">
-        <v>187.7857816752799</v>
+        <v>188.7543765395354</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3894184483754786</v>
+        <v>0.3854136926300458</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9607255998670132</v>
+        <v>0.960798508743374</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4053378492562113</v>
+        <v>0.4011389371681346</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158620442384912</v>
+        <v>0.5157886636261325</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9902544192153221</v>
+        <v>0.9902030161314199</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.348463651218236</v>
+        <v>3.350760847704133</v>
       </c>
       <c r="E17" t="n">
-        <v>56.69490661490332</v>
+        <v>56.65319667950568</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2213478840332738</v>
+        <v>-0.2186001947064831</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559247086605428</v>
+        <v>0.7559301536646212</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2928173685782677</v>
+        <v>-0.2891804138871116</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244351853252837</v>
+        <v>0.7244149414996854</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094187950553457</v>
+        <v>1.094181079311268</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.067373508468339</v>
+        <v>3.076179555515124</v>
       </c>
       <c r="E18" t="n">
-        <v>60.03572521525144</v>
+        <v>59.95312656129869</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.480966258889146</v>
+        <v>-0.4782477031190697</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7485786817122153</v>
+        <v>0.7485161117588583</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6425059524658617</v>
+        <v>-0.6389277339605774</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645494337237174</v>
+        <v>0.7645532651319736</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143554526009702</v>
+        <v>1.143481208942872</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.971979510802372</v>
+        <v>2.97740317886117</v>
       </c>
       <c r="E19" t="n">
-        <v>74.17152596412568</v>
+        <v>74.11599277394619</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1164269985158952</v>
+        <v>0.1211167475784629</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4830124867305838</v>
+        <v>0.4829833799355701</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2410434548058304</v>
+        <v>0.250767940699367</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177479863316012</v>
+        <v>0.7177315166334601</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926984120938674</v>
+        <v>0.6926507923968622</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.556991429280946</v>
+        <v>2.562154096939306</v>
       </c>
       <c r="E20" t="n">
-        <v>94.33764450505423</v>
+        <v>93.7225397314207</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.335148185891149</v>
+        <v>-0.3331318184763659</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7811124422116438</v>
+        <v>0.7810945146621914</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4290652251578654</v>
+        <v>-0.4264936089334068</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328615022723222</v>
+        <v>0.732851071763628</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143797953927516</v>
+        <v>1.143771964353511</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.5511669077325</v>
+        <v>568.0050367358192</v>
       </c>
       <c r="E2" t="n">
-        <v>10441.43502783412</v>
+        <v>10425.88969080099</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6197949258127819</v>
+        <v>0.6228723154079026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004720958888229</v>
+        <v>0.5004644676330277</v>
       </c>
       <c r="H2" t="n">
-        <v>1.238420545129585</v>
+        <v>1.244588488676947</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.910880996469</v>
+        <v>223.2251461149479</v>
       </c>
       <c r="E3" t="n">
-        <v>4340.272661670291</v>
+        <v>4368.916914475652</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2498402560127657</v>
+        <v>0.2521379934115293</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999523816884058</v>
+        <v>0.5999426393633285</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4164334764530095</v>
+        <v>0.4202701672931655</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907329914729231</v>
+        <v>0.890728598337948</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06778656407116</v>
+        <v>1.067780233770986</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.80085687169376</v>
+        <v>36.97464076837657</v>
       </c>
       <c r="E4" t="n">
-        <v>1608.390010380342</v>
+        <v>1602.999331185632</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7478177250008815</v>
+        <v>0.7597425357498258</v>
       </c>
       <c r="G4" t="n">
-        <v>1.112779686986944</v>
+        <v>1.1126959229987</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6720267576286696</v>
+        <v>0.6827943915731534</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735884890138011</v>
+        <v>0.4735598343015092</v>
       </c>
       <c r="N4" t="n">
-        <v>1.053005062409048</v>
+        <v>1.052878138213014</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.54720812834881</v>
+        <v>36.54041534342295</v>
       </c>
       <c r="E5" t="n">
-        <v>348.2509795845411</v>
+        <v>357.3987063461132</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3491914700321407</v>
+        <v>-0.3488183934883236</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634009021169566</v>
+        <v>0.5634014252233887</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.619792174134027</v>
+        <v>-0.6191294126563792</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366307761297266</v>
+        <v>0.7366406927627013</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292539128710901</v>
+        <v>0.8292784863287684</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.05606365607612</v>
+        <v>11.09942636781767</v>
       </c>
       <c r="E6" t="n">
-        <v>1274.335320696451</v>
+        <v>1260.771720776553</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4787148147310611</v>
+        <v>-0.4741045684872321</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8166209412627525</v>
+        <v>0.8162569203378971</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5862142280980667</v>
+        <v>-0.5808276250705136</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6691861543252466</v>
+        <v>0.6692903285090747</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091911880230941</v>
+        <v>1.091611688127573</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.54358632848094</v>
+        <v>10.56910524492826</v>
       </c>
       <c r="E7" t="n">
-        <v>190.8749450703483</v>
+        <v>192.0540741808466</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3327002394724179</v>
+        <v>-0.3296820917218056</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169526569877281</v>
+        <v>0.7169164037911667</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4640477111421216</v>
+        <v>-0.4598612752873206</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511367362749174</v>
+        <v>0.7511303710978312</v>
       </c>
       <c r="N7" t="n">
-        <v>1.07604296674519</v>
+        <v>1.075995838371171</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.649253103893372</v>
+        <v>9.824115961611749</v>
       </c>
       <c r="E8" t="n">
-        <v>390.0286317467279</v>
+        <v>421.7384807111516</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3440627778985386</v>
+        <v>-0.3268017522512746</v>
       </c>
       <c r="G8" t="n">
-        <v>1.172493356551668</v>
+        <v>1.173303922568152</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2934453964928516</v>
+        <v>-0.2785312023298824</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7391123766885919</v>
+        <v>0.7386348755025434</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731573765113567</v>
+        <v>1.731677776989055</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.287682569739591</v>
+        <v>7.298513480031083</v>
       </c>
       <c r="E9" t="n">
-        <v>225.5396392520842</v>
+        <v>228.8216827380348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4076425047657968</v>
+        <v>0.4114167877809045</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4816479420960339</v>
+        <v>0.4816063091292139</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8463495203401461</v>
+        <v>0.8542595476475003</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788159107329639</v>
+        <v>0.6788034022928449</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532837477900213</v>
+        <v>0.6532251984816745</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.574720341437972</v>
+        <v>6.583324087621905</v>
       </c>
       <c r="E10" t="n">
-        <v>256.0414595777519</v>
+        <v>257.2629754070118</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2844994883525452</v>
+        <v>-0.2825661464931228</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9616194967301733</v>
+        <v>0.9616131224342763</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2958545342725873</v>
+        <v>-0.2938459759968963</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713571311209043</v>
+        <v>0.7135666846714145</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371073613899069</v>
+        <v>1.371076534078939</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.564564052899226</v>
+        <v>6.568945633058722</v>
       </c>
       <c r="E11" t="n">
-        <v>361.9361741303366</v>
+        <v>364.1466605635328</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9353712173719388</v>
+        <v>0.9392081369186611</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8243598945297255</v>
+        <v>0.8243519475962477</v>
       </c>
       <c r="H11" t="n">
-        <v>1.134663662775034</v>
+        <v>1.139329068921746</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643304537366289</v>
+        <v>0.664322108998689</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09426157277082</v>
+        <v>1.094253957677325</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.266791276004766</v>
+        <v>6.268064477192902</v>
       </c>
       <c r="E12" t="n">
-        <v>93.38707204310833</v>
+        <v>93.68083030360445</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2828671279839802</v>
+        <v>-0.2823020714512758</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6606971371122401</v>
+        <v>0.6607003551037954</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.42813433280539</v>
+        <v>-0.4272770088142702</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890230107284056</v>
+        <v>0.7890418421939255</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041626992965744</v>
+        <v>1.041672804055181</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.585903690570255</v>
+        <v>4.602921181794082</v>
       </c>
       <c r="E13" t="n">
-        <v>180.2444459732875</v>
+        <v>180.9002220565925</v>
       </c>
       <c r="F13" t="n">
-        <v>1.654376832709282</v>
+        <v>1.674352726454502</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8638079613972001</v>
+        <v>0.8637424785505545</v>
       </c>
       <c r="H13" t="n">
-        <v>1.915213689433176</v>
+        <v>1.938486027993242</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040148643475722</v>
+        <v>0.6040018581700336</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042521357157917</v>
+        <v>1.042435768701706</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.570747698672552</v>
+        <v>4.568943821866271</v>
       </c>
       <c r="E14" t="n">
-        <v>139.5817238978109</v>
+        <v>139.4828793133477</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.403080532479396</v>
+        <v>-0.4024645626940226</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8534357378492193</v>
+        <v>0.8534251139621932</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4723033201014254</v>
+        <v>-0.4715874376200415</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602230038329006</v>
+        <v>0.7601998200198417</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296378930085663</v>
+        <v>1.296343017323248</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.032964108275764</v>
+        <v>4.039024088643408</v>
       </c>
       <c r="E15" t="n">
-        <v>220.2603192591197</v>
+        <v>223.0012538395748</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06341366357802913</v>
+        <v>-0.05522743016752285</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7940512321525979</v>
+        <v>0.7942224664114279</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.07986092207944906</v>
+        <v>-0.06953647435467232</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7169145466808555</v>
+        <v>0.7167995351937801</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137459778110215</v>
+        <v>1.137539888609265</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.848124734556887</v>
+        <v>3.889763997193854</v>
       </c>
       <c r="E16" t="n">
-        <v>188.7543765395354</v>
+        <v>189.3201303247301</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3854136926300458</v>
+        <v>0.4041287864493832</v>
       </c>
       <c r="G16" t="n">
-        <v>0.960798508743374</v>
+        <v>0.9605095098379178</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4011389371681346</v>
+        <v>0.420744180364834</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5157886636261325</v>
+        <v>0.5158133623194137</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9902030161314199</v>
+        <v>0.989967663743431</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.350760847704133</v>
+        <v>3.340802295336412</v>
       </c>
       <c r="E17" t="n">
-        <v>56.65319667950568</v>
+        <v>58.72965790131917</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2186001947064831</v>
+        <v>-0.2209816741025721</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559301536646212</v>
+        <v>0.7559247460503927</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2891804138871116</v>
+        <v>-0.2923329012010418</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244149414996854</v>
+        <v>0.7244541304500377</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094181079311268</v>
+        <v>1.094249122571399</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.076179555515124</v>
+        <v>3.083754419328786</v>
       </c>
       <c r="E18" t="n">
-        <v>59.95312656129869</v>
+        <v>59.7053374187188</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4782477031190697</v>
+        <v>-0.4761662635490002</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7485161117588583</v>
+        <v>0.7484857169373744</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6389277339605774</v>
+        <v>-0.6361728123515292</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645532651319736</v>
+        <v>0.7645455841263537</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143481208942872</v>
+        <v>1.143440716925639</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.97740317886117</v>
+        <v>2.967786727732252</v>
       </c>
       <c r="E19" t="n">
-        <v>74.11599277394619</v>
+        <v>75.31761390843674</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1211167475784629</v>
+        <v>0.1164269985158952</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4829833799355701</v>
+        <v>0.4830124867305838</v>
       </c>
       <c r="H19" t="n">
-        <v>0.250767940699367</v>
+        <v>0.2410434548058304</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177315166334601</v>
+        <v>0.7177076032912105</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926507923968622</v>
+        <v>0.6926800135296108</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.562154096939306</v>
+        <v>2.564198383553911</v>
       </c>
       <c r="E20" t="n">
-        <v>93.7225397314207</v>
+        <v>93.67757174883359</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3331318184763659</v>
+        <v>-0.3311138295212681</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7810945146621914</v>
+        <v>0.7810850044290423</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4264936089334068</v>
+        <v>-0.4239152302806092</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732851071763628</v>
+        <v>0.7328436896250355</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143771964353511</v>
+        <v>1.143763950443523</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.0050367358192</v>
+        <v>568.5353416198305</v>
       </c>
       <c r="E2" t="n">
-        <v>10425.88969080099</v>
+        <v>10484.56296786095</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6228723154079026</v>
+        <v>0.6246490200200641</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004644676330277</v>
+        <v>0.5004624359418063</v>
       </c>
       <c r="H2" t="n">
-        <v>1.244588488676947</v>
+        <v>1.248143667055759</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.2251461149479</v>
+        <v>223.4685921856257</v>
       </c>
       <c r="E3" t="n">
-        <v>4368.916914475652</v>
+        <v>4436.448822086273</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2521379934115293</v>
+        <v>0.2536183298246533</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999426393633285</v>
+        <v>0.5999385119006224</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4202701672931655</v>
+        <v>0.4227405388948663</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.890728598337948</v>
+        <v>0.8907270410660876</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067780233770986</v>
+        <v>1.067775355649212</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.97464076837657</v>
+        <v>36.94371150160343</v>
       </c>
       <c r="E4" t="n">
-        <v>1602.999331185632</v>
+        <v>1597.640445819288</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7597425357498258</v>
+        <v>0.7512226145059095</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1126959229987</v>
+        <v>1.11275275238607</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6827943915731534</v>
+        <v>0.6751029039425577</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735598343015092</v>
+        <v>0.4735196926367683</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052878138213014</v>
+        <v>1.052846934054085</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.54041534342295</v>
+        <v>36.58616578264854</v>
       </c>
       <c r="E5" t="n">
-        <v>357.3987063461132</v>
+        <v>357.6883961203512</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3488183934883236</v>
+        <v>-0.3484452601326762</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634014252233887</v>
+        <v>0.5634023703083325</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6191294126563792</v>
+        <v>-0.6184660883517104</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366406927627013</v>
+        <v>0.736644169601936</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292784863287684</v>
+        <v>0.8292871580791394</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.09942636781767</v>
+        <v>11.09292844311098</v>
       </c>
       <c r="E6" t="n">
-        <v>1260.771720776553</v>
+        <v>1240.368436906104</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4741045684872321</v>
+        <v>-0.4783536168911665</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8162569203378971</v>
+        <v>0.8165900883726234</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5808276250705136</v>
+        <v>-0.5857940522453243</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6692903285090747</v>
+        <v>0.6689445520941815</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091611688127573</v>
+        <v>1.091497486485661</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.56910524492826</v>
+        <v>10.60380323572991</v>
       </c>
       <c r="E7" t="n">
-        <v>192.0540741808466</v>
+        <v>189.2990316637263</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3296820917218056</v>
+        <v>-0.3290780280359775</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169164037911667</v>
+        <v>0.7169115907118367</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4598612752873206</v>
+        <v>-0.4590217710237171</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511303710978312</v>
+        <v>0.7511244004990321</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075995838371171</v>
+        <v>1.075984429822124</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.824115961611749</v>
+        <v>9.909544148466189</v>
       </c>
       <c r="E8" t="n">
-        <v>421.7384807111516</v>
+        <v>442.7175216159536</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3268017522512746</v>
+        <v>-0.3237877052015968</v>
       </c>
       <c r="G8" t="n">
-        <v>1.173303922568152</v>
+        <v>1.173490495693302</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2785312023298824</v>
+        <v>-0.2759184726164331</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7386348755025434</v>
+        <v>0.7386002125275068</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731677776989055</v>
+        <v>1.731878892942259</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.298513480031083</v>
+        <v>7.310537527726649</v>
       </c>
       <c r="E9" t="n">
-        <v>228.8216827380348</v>
+        <v>228.695586752651</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4114167877809045</v>
+        <v>0.4121247647654609</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4816063091292139</v>
+        <v>0.481599687658454</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8542595476475003</v>
+        <v>0.8557413456167686</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6788034022928449</v>
+        <v>0.6787845283375272</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532251984816745</v>
+        <v>0.6532007067015043</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.583324087621905</v>
+        <v>6.584763633208951</v>
       </c>
       <c r="E10" t="n">
-        <v>257.2629754070118</v>
+        <v>253.5667369206289</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2825661464931228</v>
+        <v>-0.2846375311344406</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9616131224342763</v>
+        <v>0.9616201610414969</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2938459759968963</v>
+        <v>-0.2959978821847492</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7135666846714145</v>
+        <v>0.7135645887933271</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371076534078939</v>
+        <v>1.371088108736171</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.568945633058722</v>
+        <v>6.568309425897932</v>
       </c>
       <c r="E11" t="n">
-        <v>364.1466605635328</v>
+        <v>360.1000369553503</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9392081369186611</v>
+        <v>0.9374370000297931</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8243519475962477</v>
+        <v>0.8243551877482279</v>
       </c>
       <c r="H11" t="n">
-        <v>1.139329068921746</v>
+        <v>1.137176078906538</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.664322108998689</v>
+        <v>0.6643164906455409</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094253957677325</v>
+        <v>1.094253446494488</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.268064477192902</v>
+        <v>6.296782138391722</v>
       </c>
       <c r="E12" t="n">
-        <v>93.68083030360445</v>
+        <v>91.97533698995205</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2823020714512758</v>
+        <v>-0.2789092504682925</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6607003551037954</v>
+        <v>0.6607340105749231</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4272770088142702</v>
+        <v>-0.4221203177139403</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890418421939255</v>
+        <v>0.7890070956776826</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041672804055181</v>
+        <v>1.041684220950814</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.602921181794082</v>
+        <v>4.612360502288311</v>
       </c>
       <c r="E13" t="n">
-        <v>180.9002220565925</v>
+        <v>181.7133957256311</v>
       </c>
       <c r="F13" t="n">
-        <v>1.674352726454502</v>
+        <v>1.67589098113461</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8637424785505545</v>
+        <v>0.8637393777158284</v>
       </c>
       <c r="H13" t="n">
-        <v>1.938486027993242</v>
+        <v>1.940273911751631</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6040018581700336</v>
+        <v>0.6039934334309671</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042435768701706</v>
+        <v>1.042421718134251</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.568943821866271</v>
+        <v>4.56847502013237</v>
       </c>
       <c r="E14" t="n">
-        <v>139.4828793133477</v>
+        <v>139.02011129258</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4024645626940226</v>
+        <v>-0.4036963333907216</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8534251139621932</v>
+        <v>0.8534472473943604</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4715874376200415</v>
+        <v>-0.4730184960151168</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601998200198417</v>
+        <v>0.7601639345820959</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296343017323248</v>
+        <v>1.296320704503373</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.039024088643408</v>
+        <v>4.06776065149948</v>
       </c>
       <c r="E15" t="n">
-        <v>223.0012538395748</v>
+        <v>250.5189093553048</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05522743016752285</v>
+        <v>-0.05061436592135715</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7942224664114279</v>
+        <v>0.7943501048737969</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06953647435467232</v>
+        <v>-0.06371795712093291</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7167995351937801</v>
+        <v>0.716731781938197</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137539888609265</v>
+        <v>1.137619779749449</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.889763997193854</v>
+        <v>3.865454275398507</v>
       </c>
       <c r="E16" t="n">
-        <v>189.3201303247301</v>
+        <v>190.3845640777873</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4041287864493832</v>
+        <v>0.3867482698503573</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9605095098379178</v>
+        <v>0.9607735404982056</v>
       </c>
       <c r="H16" t="n">
-        <v>0.420744180364834</v>
+        <v>0.4025384271613167</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5158133623194137</v>
+        <v>0.5156500299055756</v>
       </c>
       <c r="N16" t="n">
-        <v>0.989967663743431</v>
+        <v>0.9899302511247683</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.340802295336412</v>
+        <v>3.352620210770496</v>
       </c>
       <c r="E17" t="n">
-        <v>58.72965790131917</v>
+        <v>59.24157983127397</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2209816741025721</v>
+        <v>-0.2191499383141915</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559247460503927</v>
+        <v>0.7559281112072561</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2923329012010418</v>
+        <v>-0.2899084384680413</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244541304500377</v>
+        <v>0.7244512060744112</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094249122571399</v>
+        <v>1.094254018963627</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.083754419328786</v>
+        <v>3.08332039147827</v>
       </c>
       <c r="E18" t="n">
-        <v>59.7053374187188</v>
+        <v>59.85707522998678</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4761662635490002</v>
+        <v>-0.4778475973482562</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7484857169373744</v>
+        <v>0.7485090918034846</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6361728123515292</v>
+        <v>-0.638399189242863</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645455841263537</v>
+        <v>0.7645167161359083</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143440716925639</v>
+        <v>1.143437892169817</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.967786727732252</v>
+        <v>2.972307828523401</v>
       </c>
       <c r="E19" t="n">
-        <v>75.31761390843674</v>
+        <v>76.06055175709668</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1164269985158952</v>
+        <v>0.1154896759196997</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4830124867305838</v>
+        <v>0.4830214518736785</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2410434548058304</v>
+        <v>0.2390984406007355</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177076032912105</v>
+        <v>0.7176769457524321</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926800135296108</v>
+        <v>0.6926660932328514</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.564198383553911</v>
+        <v>2.564970953207887</v>
       </c>
       <c r="E20" t="n">
-        <v>93.67757174883359</v>
+        <v>93.47597850161023</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3311138295212681</v>
+        <v>-0.3316184786538651</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7810850044290423</v>
+        <v>0.7810865928424613</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4239152302806092</v>
+        <v>-0.4245604542347455</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328436896250355</v>
+        <v>0.7328423501208523</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143763950443523</v>
+        <v>1.143768829061766</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.5353416198305</v>
+        <v>569.6097010043535</v>
       </c>
       <c r="E2" t="n">
-        <v>10484.56296786095</v>
+        <v>10241.05134796151</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6246490200200641</v>
+        <v>0.62962578313705</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004624359418063</v>
+        <v>0.5004659759641956</v>
       </c>
       <c r="H2" t="n">
-        <v>1.248143667055759</v>
+        <v>1.258079097033551</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.4685921856257</v>
+        <v>223.6161150889672</v>
       </c>
       <c r="E3" t="n">
-        <v>4436.448822086273</v>
+        <v>4334.340961021198</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2536183298246533</v>
+        <v>0.2558075043571211</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999385119006224</v>
+        <v>0.5999354910980014</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4227405388948663</v>
+        <v>0.4263916840274651</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907270410660876</v>
+        <v>0.8907179797745666</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067775355649212</v>
+        <v>1.067751564122521</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.94371150160343</v>
+        <v>36.97581486607695</v>
       </c>
       <c r="E4" t="n">
-        <v>1597.640445819288</v>
+        <v>1497.902072350176</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7512226145059095</v>
+        <v>0.7604246039611506</v>
       </c>
       <c r="G4" t="n">
-        <v>1.11275275238607</v>
+        <v>1.112692025136847</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6751029039425577</v>
+        <v>0.6834097726795771</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4735196926367683</v>
+        <v>0.4734758581173334</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052846934054085</v>
+        <v>1.052684571427634</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.58616578264854</v>
+        <v>36.62791358476724</v>
       </c>
       <c r="E5" t="n">
-        <v>357.6883961203512</v>
+        <v>350.2710950989306</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3484452601326762</v>
+        <v>-0.3469521588965258</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634023703083325</v>
+        <v>0.5634103703765341</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6184660883517104</v>
+        <v>-0.6158071933689353</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.736644169601936</v>
+        <v>0.7366545778626169</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292871580791394</v>
+        <v>0.8293047849127689</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.09292844311098</v>
+        <v>11.05246353256956</v>
       </c>
       <c r="E6" t="n">
-        <v>1240.368436906104</v>
+        <v>1228.381991105638</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4783536168911665</v>
+        <v>-0.4770889010847916</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8165900883726234</v>
+        <v>0.8164851883117809</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5857940522453243</v>
+        <v>-0.5843203378511402</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6689445520941815</v>
+        <v>0.6687532126568833</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091497486485661</v>
+        <v>1.091037391139908</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.60380323572991</v>
+        <v>10.60647447839192</v>
       </c>
       <c r="E7" t="n">
-        <v>189.2990316637263</v>
+        <v>186.2126152534228</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3290780280359775</v>
+        <v>-0.3272649698060519</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169115907118367</v>
+        <v>0.7169020269132483</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4590217710237171</v>
+        <v>-0.4564988764436203</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511244004990321</v>
+        <v>0.7511116698127308</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075984429822124</v>
+        <v>1.075944228755053</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.909544148466189</v>
+        <v>9.905822806547977</v>
       </c>
       <c r="E8" t="n">
-        <v>442.7175216159536</v>
+        <v>436.9199685783825</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3237877052015968</v>
+        <v>-0.3188822583853462</v>
       </c>
       <c r="G8" t="n">
-        <v>1.173490495693302</v>
+        <v>1.173822461426682</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2759184726164331</v>
+        <v>-0.2716614043982186</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7386002125275068</v>
+        <v>0.7386608060816974</v>
       </c>
       <c r="N8" t="n">
-        <v>1.731878892942259</v>
+        <v>1.732498685617472</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.310537527726649</v>
+        <v>7.316768309811216</v>
       </c>
       <c r="E9" t="n">
-        <v>228.695586752651</v>
+        <v>223.8439215415329</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4121247647654609</v>
+        <v>0.4168470212054203</v>
       </c>
       <c r="G9" t="n">
-        <v>0.481599687658454</v>
+        <v>0.4815651070185836</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8557413456167686</v>
+        <v>0.8656088556460427</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6787845283375272</v>
+        <v>0.6787727541224724</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532007067015043</v>
+        <v>0.6531378548772162</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.584763633208951</v>
+        <v>6.590435725826449</v>
       </c>
       <c r="E10" t="n">
-        <v>253.5667369206289</v>
+        <v>249.2325574419296</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2846375311344406</v>
+        <v>-0.2755115541052253</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9616201610414969</v>
+        <v>0.9616360921127302</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2959978821847492</v>
+        <v>-0.2865029259664349</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7135645887933271</v>
+        <v>0.7135706522459657</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371088108736171</v>
+        <v>1.371112775748883</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.568309425897932</v>
+        <v>6.57462948209552</v>
       </c>
       <c r="E11" t="n">
-        <v>360.1000369553503</v>
+        <v>352.6854367431771</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9374370000297931</v>
+        <v>0.9445241268243352</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8243551877482279</v>
+        <v>0.8243466260446493</v>
       </c>
       <c r="H11" t="n">
-        <v>1.137176078906538</v>
+        <v>1.145785155155323</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643164906455409</v>
+        <v>0.6643094583971918</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094253446494488</v>
+        <v>1.094222758348814</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.296782138391722</v>
+        <v>6.296942360194212</v>
       </c>
       <c r="E12" t="n">
-        <v>91.97533698995205</v>
+        <v>90.5060738808766</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2789092504682925</v>
+        <v>-0.2773999660111648</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6607340105749231</v>
+        <v>0.6607568628139693</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4221203177139403</v>
+        <v>-0.419821543479397</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890070956776826</v>
+        <v>0.7890443902228401</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041684220950814</v>
+        <v>1.041762119592931</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.612360502288311</v>
+        <v>4.616173652662266</v>
       </c>
       <c r="E13" t="n">
-        <v>181.7133957256311</v>
+        <v>174.4451827504448</v>
       </c>
       <c r="F13" t="n">
-        <v>1.67589098113461</v>
+        <v>1.688205474540331</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8637393777158284</v>
+        <v>0.8637245300641833</v>
       </c>
       <c r="H13" t="n">
-        <v>1.940273911751631</v>
+        <v>1.954564697166677</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6039934334309671</v>
+        <v>0.6039858963249477</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042421718134251</v>
+        <v>1.04238341770107</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.56847502013237</v>
+        <v>4.56734557908308</v>
       </c>
       <c r="E14" t="n">
-        <v>139.02011129258</v>
+        <v>137.3919122503416</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4036963333907216</v>
+        <v>-0.4012321168273499</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8534472473943604</v>
+        <v>0.8534065232920333</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4730184960151168</v>
+        <v>-0.4701535620791704</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601639345820959</v>
+        <v>0.760139323407681</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296320704503373</v>
+        <v>1.296207711137824</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.06776065149948</v>
+        <v>4.064937944137301</v>
       </c>
       <c r="E15" t="n">
-        <v>250.5189093553048</v>
+        <v>251.8191725385496</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05061436592135715</v>
+        <v>-0.04941741211793493</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7943501048737969</v>
+        <v>0.79438687562292</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06371795712093291</v>
+        <v>-0.06220824340682136</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.716731781938197</v>
+        <v>0.7168700450993153</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137619779749449</v>
+        <v>1.137883857652789</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.865454275398507</v>
+        <v>3.846780353023834</v>
       </c>
       <c r="E16" t="n">
-        <v>190.3845640777873</v>
+        <v>182.0937773913449</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3867482698503573</v>
+        <v>0.3894184483754786</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9607735404982056</v>
+        <v>0.9607255998670132</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4025384271613167</v>
+        <v>0.4053378492562113</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5156500299055756</v>
+        <v>0.5155181569376814</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9899302511247683</v>
+        <v>0.9896207022107806</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.352620210770496</v>
+        <v>3.342871206601129</v>
       </c>
       <c r="E17" t="n">
-        <v>59.24157983127397</v>
+        <v>60.42299172682414</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2191499383141915</v>
+        <v>-0.2198827698162474</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559281112072561</v>
+        <v>0.7559261295047169</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2899084384680413</v>
+        <v>-0.2908786470449364</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244512060744112</v>
+        <v>0.7244594496986042</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094254018963627</v>
+        <v>1.094255861727076</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.08332039147827</v>
+        <v>3.083293897596138</v>
       </c>
       <c r="E18" t="n">
-        <v>59.85707522998678</v>
+        <v>59.46691368833096</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4778475973482562</v>
+        <v>-0.4758458466853965</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7485090918034846</v>
+        <v>0.7484823834867552</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.638399189242863</v>
+        <v>-0.63574755690134</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645167161359083</v>
+        <v>0.7645014266141137</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143437892169817</v>
+        <v>1.143366137665458</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.972307828523401</v>
+        <v>2.970893312861926</v>
       </c>
       <c r="E19" t="n">
-        <v>76.06055175709668</v>
+        <v>76.52108944967247</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1154896759196997</v>
+        <v>0.1192402210656878</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4830214518736785</v>
+        <v>0.4829918786974565</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2390984406007355</v>
+        <v>0.2468783147808976</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7176769457524321</v>
+        <v>0.7176696391415476</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926660932328514</v>
+        <v>0.6926117337453135</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.564970953207887</v>
+        <v>2.566396505913356</v>
       </c>
       <c r="E20" t="n">
-        <v>93.47597850161023</v>
+        <v>91.64929784318656</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3316184786538651</v>
+        <v>-0.3295992750492626</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7810865928424613</v>
+        <v>0.7810833958131922</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4245604542347455</v>
+        <v>-0.421977060088589</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328423501208523</v>
+        <v>0.7328381214978356</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143768829061766</v>
+        <v>1.143749457529239</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>569.6097010043535</v>
+        <v>569.4995672790687</v>
       </c>
       <c r="E2" t="n">
-        <v>10241.05134796151</v>
+        <v>10285.2315338799</v>
       </c>
       <c r="F2" t="n">
-        <v>0.62962578313705</v>
+        <v>0.6263785897522653</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004659759641956</v>
+        <v>0.5004621245951304</v>
       </c>
       <c r="H2" t="n">
-        <v>1.258079097033551</v>
+        <v>1.251600388858598</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.6161150889672</v>
+        <v>223.8717103088233</v>
       </c>
       <c r="E3" t="n">
-        <v>4334.340961021198</v>
+        <v>4393.912677433581</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2558075043571211</v>
+        <v>0.2549151552181546</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999354910980014</v>
+        <v>0.5999362785658782</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4263916840274651</v>
+        <v>0.4249037178206963</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907179797745666</v>
+        <v>0.8907258073366208</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067751564122521</v>
+        <v>1.067770566071163</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.97581486607695</v>
+        <v>36.88190065488742</v>
       </c>
       <c r="E4" t="n">
-        <v>1497.902072350176</v>
+        <v>1351.69223286613</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7604246039611506</v>
+        <v>0.7467966016332013</v>
       </c>
       <c r="G4" t="n">
-        <v>1.112692025136847</v>
+        <v>1.112788235643361</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6834097726795771</v>
+        <v>0.6711039690327416</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4734758581173334</v>
+        <v>0.4734752928779855</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052684571427634</v>
+        <v>1.052782438248762</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.62791358476724</v>
+        <v>36.54462530816243</v>
       </c>
       <c r="E5" t="n">
-        <v>350.2710950989306</v>
+        <v>349.3412282730757</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3469521588965258</v>
+        <v>-0.3510560000394733</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634103703765341</v>
+        <v>0.5634046162704283</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6158071933689353</v>
+        <v>-0.6230974860720172</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366545778626169</v>
+        <v>0.7366425788177478</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8293047849127689</v>
+        <v>0.8292891890330877</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.05246353256956</v>
+        <v>10.92479410501702</v>
       </c>
       <c r="E6" t="n">
-        <v>1228.381991105638</v>
+        <v>1022.779692486564</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4770889010847916</v>
+        <v>-0.4882622597628599</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8164851883117809</v>
+        <v>0.8175811086575265</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5843203378511402</v>
+        <v>-0.5972034512448431</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6687532126568833</v>
+        <v>0.6680254362562935</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091037391139908</v>
+        <v>1.09132130074317</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.60647447839192</v>
+        <v>10.64415874130691</v>
       </c>
       <c r="E7" t="n">
-        <v>186.2126152534228</v>
+        <v>182.2852789712586</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3272649698060519</v>
+        <v>-0.3266603282082257</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7169020269132483</v>
+        <v>0.716900464162986</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4564988764436203</v>
+        <v>-0.455656460746774</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511116698127308</v>
+        <v>0.7511284595032167</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075944228755053</v>
+        <v>1.075974214231525</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.905822806547977</v>
+        <v>9.965485621739873</v>
       </c>
       <c r="E8" t="n">
-        <v>436.9199685783825</v>
+        <v>487.6328276190802</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3188822583853462</v>
+        <v>-0.3162369655591513</v>
       </c>
       <c r="G8" t="n">
-        <v>1.173822461426682</v>
+        <v>1.174015964468157</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2716614043982186</v>
+        <v>-0.2693634287182885</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7386608060816974</v>
+        <v>0.7383627392683225</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732498685617472</v>
+        <v>1.732098396398576</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.316768309811216</v>
+        <v>7.304186112819155</v>
       </c>
       <c r="E9" t="n">
-        <v>223.8439215415329</v>
+        <v>217.9903459022537</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4168470212054203</v>
+        <v>0.4083499782219282</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4815651070185836</v>
+        <v>0.4816393253917362</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8656088556460427</v>
+        <v>0.847833548246504</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6787727541224724</v>
+        <v>0.6786989820003824</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531378548772162</v>
+        <v>0.6531725454731903</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.590435725826449</v>
+        <v>6.645378731669334</v>
       </c>
       <c r="E10" t="n">
-        <v>249.2325574419296</v>
+        <v>298.5066808714164</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2755115541052253</v>
+        <v>-0.2763424577478156</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9616360921127302</v>
+        <v>0.9616296277612683</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2865029259664349</v>
+        <v>-0.2873689097861487</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7135706522459657</v>
+        <v>0.713556247809232</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371112775748883</v>
+        <v>1.371086432410105</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.57462948209552</v>
+        <v>6.545529479017751</v>
       </c>
       <c r="E11" t="n">
-        <v>352.6854367431771</v>
+        <v>340.847867029358</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9445241268243352</v>
+        <v>0.9250510971799124</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8243466260446493</v>
+        <v>0.8243983959440251</v>
       </c>
       <c r="H11" t="n">
-        <v>1.145785155155323</v>
+        <v>1.122092306015017</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6643094583971918</v>
+        <v>0.6642699652879698</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094222758348814</v>
+        <v>1.094234842047673</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.296942360194212</v>
+        <v>6.290879283023866</v>
       </c>
       <c r="E12" t="n">
-        <v>90.5060738808766</v>
+        <v>89.89659887847949</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2773999660111648</v>
+        <v>-0.2807946760237362</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6607568628139693</v>
+        <v>0.6607122766604644</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.419821543479397</v>
+        <v>-0.4249878289578607</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890443902228401</v>
+        <v>0.7890522892667775</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041762119592931</v>
+        <v>1.041710269018581</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.616173652662266</v>
+        <v>4.70063738421295</v>
       </c>
       <c r="E13" t="n">
-        <v>174.4451827504448</v>
+        <v>185.0550704814673</v>
       </c>
       <c r="F13" t="n">
-        <v>1.688205474540331</v>
+        <v>1.740709139069085</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8637245300641833</v>
+        <v>0.8638589440387177</v>
       </c>
       <c r="H13" t="n">
-        <v>1.954564697166677</v>
+        <v>2.015038625323381</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6039858963249477</v>
+        <v>0.6039126033470826</v>
       </c>
       <c r="N13" t="n">
-        <v>1.04238341770107</v>
+        <v>1.042427145193316</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.56734557908308</v>
+        <v>4.548237501973937</v>
       </c>
       <c r="E14" t="n">
-        <v>137.3919122503416</v>
+        <v>107.2039992115459</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4012321168273499</v>
+        <v>-0.4080022044226658</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8534065232920333</v>
+        <v>0.8535526092806957</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4701535620791704</v>
+        <v>-0.4780047532939963</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.760139323407681</v>
+        <v>0.7600416546032767</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296207711137824</v>
+        <v>1.296272995630719</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.064937944137301</v>
+        <v>4.03882767372596</v>
       </c>
       <c r="E15" t="n">
-        <v>251.8191725385496</v>
+        <v>246.9512460019594</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04941741211793493</v>
+        <v>-0.06119842869565517</v>
       </c>
       <c r="G15" t="n">
-        <v>0.79438687562292</v>
+        <v>0.7940905688159561</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06220824340682136</v>
+        <v>-0.07706731586915364</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7168700450993153</v>
+        <v>0.717019069612985</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137883857652789</v>
+        <v>1.137704639090291</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.846780353023834</v>
+        <v>3.886066522782189</v>
       </c>
       <c r="E16" t="n">
-        <v>182.0937773913449</v>
+        <v>161.0673204918768</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3894184483754786</v>
+        <v>0.4027897828134952</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9607255998670132</v>
+        <v>0.9605258260351627</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4053378492562113</v>
+        <v>0.4193430014017655</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5155181569376814</v>
+        <v>0.5157331323502012</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9896207022107806</v>
+        <v>0.9898351316098755</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.342871206601129</v>
+        <v>3.340613663384961</v>
       </c>
       <c r="E17" t="n">
-        <v>60.42299172682414</v>
+        <v>61.88873876408979</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2198827698162474</v>
+        <v>-0.2257388305780088</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559261295047169</v>
+        <v>0.7559407865307429</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2908786470449364</v>
+        <v>-0.2986197260422968</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244594496986042</v>
+        <v>0.7244395928355434</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094255861727076</v>
+        <v>1.09425550643846</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.083293897596138</v>
+        <v>3.077255508040275</v>
       </c>
       <c r="E18" t="n">
-        <v>59.46691368833096</v>
+        <v>59.51946960709709</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4758458466853965</v>
+        <v>-0.4803269383284361</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7484823834867552</v>
+        <v>0.748561632598336</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.63574755690134</v>
+        <v>-0.641666520712758</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645014266141137</v>
+        <v>0.7644416428776216</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143366137665458</v>
+        <v>1.143406575835398</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.970893312861926</v>
+        <v>2.966403618866997</v>
       </c>
       <c r="E19" t="n">
-        <v>76.52108944967247</v>
+        <v>81.58504703060117</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1192402210656878</v>
+        <v>0.1136156586017614</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4829918786974565</v>
+        <v>0.4830425255180984</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2468783147808976</v>
+        <v>0.2352083980181668</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7176696391415476</v>
+        <v>0.7176202584547619</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926117337453135</v>
+        <v>0.6926420301783447</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.566396505913356</v>
+        <v>2.563212490509865</v>
       </c>
       <c r="E20" t="n">
-        <v>91.64929784318656</v>
+        <v>88.55660646885171</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3295992750492626</v>
+        <v>-0.3336360624392493</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7810833958131922</v>
+        <v>0.7810982074441402</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.421977060088589</v>
+        <v>-0.4271371503091166</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328381214978356</v>
+        <v>0.7328248283234107</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143749457529239</v>
+        <v>1.143759201032543</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>569.4995672790687</v>
+        <v>573.7259535769668</v>
       </c>
       <c r="E2" t="n">
-        <v>10285.2315338799</v>
+        <v>12018.66453767093</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6263785897522653</v>
+        <v>0.6415557120419584</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5004621245951304</v>
+        <v>0.5005296844398317</v>
       </c>
       <c r="H2" t="n">
-        <v>1.251600388858598</v>
+        <v>1.281753574235974</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.8717103088233</v>
+        <v>226.5240386458644</v>
       </c>
       <c r="E3" t="n">
-        <v>4393.912677433581</v>
+        <v>5347.67842226778</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2549151552181546</v>
+        <v>0.2736436319080253</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5999362785658782</v>
+        <v>0.6000473292122276</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4249037178206963</v>
+        <v>0.4560367467467583</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907258073366208</v>
+        <v>0.8907594228276654</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067770566071163</v>
+        <v>1.067864363002865</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.88190065488742</v>
+        <v>37.59462679973645</v>
       </c>
       <c r="E4" t="n">
-        <v>1351.69223286613</v>
+        <v>1563.630182805716</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7467966016332013</v>
+        <v>0.8045658032321528</v>
       </c>
       <c r="G4" t="n">
-        <v>1.112788235643361</v>
+        <v>1.112643591805591</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6711039690327416</v>
+        <v>0.7231118834077929</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4734752928779855</v>
+        <v>0.4736009135684766</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052782438248762</v>
+        <v>1.052782757819798</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.54462530816243</v>
+        <v>36.81792292121363</v>
       </c>
       <c r="E5" t="n">
-        <v>349.3412282730757</v>
+        <v>377.486030660453</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3510560000394733</v>
+        <v>-0.3432154364294911</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634046162704283</v>
+        <v>0.5634599063267443</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6230974860720172</v>
+        <v>-0.6091213102755607</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7366425788177478</v>
+        <v>0.7367110838418602</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8292891890330877</v>
+        <v>0.8293357441047204</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.92479410501702</v>
+        <v>11.07727721755248</v>
       </c>
       <c r="E6" t="n">
-        <v>1022.779692486564</v>
+        <v>901.3546769876833</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4882622597628599</v>
+        <v>-0.477450331500709</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8175811086575265</v>
+        <v>0.8165146700032047</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5972034512448431</v>
+        <v>-0.584741890184086</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6680254362562935</v>
+        <v>0.6679874703736165</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09132130074317</v>
+        <v>1.08968875552066</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.64415874130691</v>
+        <v>10.79599784915324</v>
       </c>
       <c r="E7" t="n">
-        <v>182.2852789712586</v>
+        <v>204.0417392459941</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3266603282082257</v>
+        <v>-0.3121057708462645</v>
       </c>
       <c r="G7" t="n">
-        <v>0.716900464162986</v>
+        <v>0.7171067098149697</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.455656460746774</v>
+        <v>-0.4352291877547695</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7511284595032167</v>
+        <v>0.7512069581471744</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075974214231525</v>
+        <v>1.076250953527189</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.965485621739873</v>
+        <v>10.27914456599434</v>
       </c>
       <c r="E8" t="n">
-        <v>487.6328276190802</v>
+        <v>654.540525517875</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3162369655591513</v>
+        <v>-0.2869601318067684</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174015964468157</v>
+        <v>1.176824310076767</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2693634287182885</v>
+        <v>-0.2438427973909285</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7383627392683225</v>
+        <v>0.7379395597618746</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732098396398576</v>
+        <v>1.735012408438913</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.304186112819155</v>
+        <v>7.356492262808532</v>
       </c>
       <c r="E9" t="n">
-        <v>217.9903459022537</v>
+        <v>224.9158832917074</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4083499782219282</v>
+        <v>0.424411336498673</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4816393253917362</v>
+        <v>0.4815443749341073</v>
       </c>
       <c r="H9" t="n">
-        <v>0.847833548246504</v>
+        <v>0.8813545720615008</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6786989820003824</v>
+        <v>0.6787543880674897</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6531725454731903</v>
+        <v>0.653008937724716</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.645378731669334</v>
+        <v>6.768275834455268</v>
       </c>
       <c r="E10" t="n">
-        <v>298.5066808714164</v>
+        <v>326.7948675360155</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2763424577478156</v>
+        <v>-0.2575860757166096</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9616296277612683</v>
+        <v>0.9620176515289415</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2873689097861487</v>
+        <v>-0.2677560804702764</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713556247809232</v>
+        <v>0.713646156817675</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371086432410105</v>
+        <v>1.371627340289989</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.545529479017751</v>
+        <v>6.580451799246024</v>
       </c>
       <c r="E11" t="n">
-        <v>340.847867029358</v>
+        <v>370.5804213961928</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9250510971799124</v>
+        <v>0.9406844128028362</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8243983959440251</v>
+        <v>0.8243498075118239</v>
       </c>
       <c r="H11" t="n">
-        <v>1.122092306015017</v>
+        <v>1.141122863414199</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6642699652879698</v>
+        <v>0.6641779308553243</v>
       </c>
       <c r="N11" t="n">
-        <v>1.094234842047673</v>
+        <v>1.093871085921587</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.290879283023866</v>
+        <v>6.394276194482449</v>
       </c>
       <c r="E12" t="n">
-        <v>89.89659887847949</v>
+        <v>97.81723656269234</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2807946760237362</v>
+        <v>-0.2666220996274928</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6607122766604644</v>
+        <v>0.6610602378797483</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4249878289578607</v>
+        <v>-0.4033249685121635</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890522892667775</v>
+        <v>0.7890753219147589</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041710269018581</v>
+        <v>1.042148620203791</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.70063738421295</v>
+        <v>4.709280400855604</v>
       </c>
       <c r="E13" t="n">
-        <v>185.0550704814673</v>
+        <v>222.2537858005373</v>
       </c>
       <c r="F13" t="n">
-        <v>1.740709139069085</v>
+        <v>1.748452984952623</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8638589440387177</v>
+        <v>0.863905677093221</v>
       </c>
       <c r="H13" t="n">
-        <v>2.015038625323381</v>
+        <v>2.023893384791305</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6039126033470826</v>
+        <v>0.6041260398950588</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042427145193316</v>
+        <v>1.042711215278432</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.548237501973937</v>
+        <v>4.629563532340897</v>
       </c>
       <c r="E14" t="n">
-        <v>107.2039992115459</v>
+        <v>117.9744394970595</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4080022044226658</v>
+        <v>-0.393823299425188</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8535526092806957</v>
+        <v>0.8533693871506876</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4780047532939963</v>
+        <v>-0.4614921807074934</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7600416546032767</v>
+        <v>0.7601559596981815</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296272995630719</v>
+        <v>1.296014693299492</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.03882767372596</v>
+        <v>4.196433217410772</v>
       </c>
       <c r="E15" t="n">
-        <v>246.9512460019594</v>
+        <v>310.931591013234</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06119842869565517</v>
+        <v>-0.01280532735254247</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7940905688159561</v>
+        <v>0.7962286727924539</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.07706731586915364</v>
+        <v>-0.01608247453289129</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.717019069612985</v>
+        <v>0.7162359274479307</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137704639090291</v>
+        <v>1.139368152672856</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.886066522782189</v>
+        <v>4.016186136109154</v>
       </c>
       <c r="E16" t="n">
-        <v>161.0673204918768</v>
+        <v>183.1151341118216</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4027897828134952</v>
+        <v>0.4715086229362375</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9605258260351627</v>
+        <v>0.9605429500828886</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4193430014017655</v>
+        <v>0.4908771886728744</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5157331323502012</v>
+        <v>0.5160220173154255</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9898351316098755</v>
+        <v>0.9902735566514943</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.340613663384961</v>
+        <v>3.375097111878841</v>
       </c>
       <c r="E17" t="n">
-        <v>61.88873876408979</v>
+        <v>68.18596457916848</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2257388305780088</v>
+        <v>-0.211444185004565</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7559407865307429</v>
+        <v>0.756000084665752</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2986197260422968</v>
+        <v>-0.2796880440801143</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7244395928355434</v>
+        <v>0.7245208196716985</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09425550643846</v>
+        <v>1.094316317376671</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.077255508040275</v>
+        <v>3.117525896858629</v>
       </c>
       <c r="E18" t="n">
-        <v>59.51946960709709</v>
+        <v>66.8952352951906</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4803269383284361</v>
+        <v>-0.4698284071609558</v>
       </c>
       <c r="G18" t="n">
-        <v>0.748561632598336</v>
+        <v>0.7484861811043073</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.641666520712758</v>
+        <v>-0.6277048515014355</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644416428776216</v>
+        <v>0.7645374163475918</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143406575835398</v>
+        <v>1.143280226653874</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.966403618866997</v>
+        <v>2.991420957180464</v>
       </c>
       <c r="E19" t="n">
-        <v>81.58504703060117</v>
+        <v>90.39794395986696</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1136156586017614</v>
+        <v>0.127691162378412</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4830425255180984</v>
+        <v>0.4829866484339556</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2352083980181668</v>
+        <v>0.2643782448074706</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7176202584547619</v>
+        <v>0.7177111155551203</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926420301783447</v>
+        <v>0.692556100111647</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.563212490509865</v>
+        <v>2.590382890754003</v>
       </c>
       <c r="E20" t="n">
-        <v>88.55660646885171</v>
+        <v>96.735542566422</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3336360624392493</v>
+        <v>-0.3230257040484199</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7810982074441402</v>
+        <v>0.781131138726652</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4271371503091166</v>
+        <v>-0.4135358175261006</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328248283234107</v>
+        <v>0.7328803653368163</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143759201032543</v>
+        <v>1.143739706400508</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-26.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>573.7259535769668</v>
+        <v>572.7314136672076</v>
       </c>
       <c r="E2" t="n">
-        <v>12018.66453767093</v>
+        <v>13074.39519018865</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6415557120419584</v>
+        <v>0.6400045526424001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5005296844398317</v>
+        <v>0.5005170046860884</v>
       </c>
       <c r="H2" t="n">
-        <v>1.281753574235974</v>
+        <v>1.278686931014052</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.5240386458644</v>
+        <v>225.2785417693903</v>
       </c>
       <c r="E3" t="n">
-        <v>5347.67842226778</v>
+        <v>5609.47792516448</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2736436319080253</v>
+        <v>0.2650167950706306</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6000473292122276</v>
+        <v>0.5999629605449365</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4560367467467583</v>
+        <v>0.4417219270168282</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907594228276654</v>
+        <v>0.8907318435504589</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067864363002865</v>
+        <v>1.067708207523036</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.59462679973645</v>
+        <v>37.78618685954187</v>
       </c>
       <c r="E4" t="n">
-        <v>1563.630182805716</v>
+        <v>1692.615210157843</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8045658032321528</v>
+        <v>0.8079997073827372</v>
       </c>
       <c r="G4" t="n">
-        <v>1.112643591805591</v>
+        <v>1.112656533667011</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7231118834077929</v>
+        <v>0.7261896937052006</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4736009135684766</v>
+        <v>0.4736175374011359</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052782757819798</v>
+        <v>1.052858629207131</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.81792292121363</v>
+        <v>36.77314842493362</v>
       </c>
       <c r="E5" t="n">
-        <v>377.486030660453</v>
+        <v>412.6287925483452</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3432154364294911</v>
+        <v>-0.3439632340807874</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5634599063267443</v>
+        <v>0.563446623929636</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6091213102755607</v>
+        <v>-0.6104628539290743</v>
       </c>
       <c r="I5" t="n">
         <v>0.3496897913141569</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7367110838418602</v>
+        <v>0.7366979864470108</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8293357441047204</v>
+        <v>0.829322459443037</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.07727721755248</v>
+        <v>10.98671889641463</v>
       </c>
       <c r="E6" t="n">
-        <v>901.3546769876833</v>
+        <v>864.3803595936787</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.477450331500709</v>
+        <v>-0.4834043273803299</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8165146700032047</v>
+        <v>0.8170576540861468</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.584741890184086</v>
+        <v>-0.5916404123537675</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6679874703736165</v>
+        <v>0.6674758367969167</v>
       </c>
       <c r="N6" t="n">
-        <v>1.08968875552066</v>
+        <v>1.089605820114975</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.79599784915324</v>
+        <v>10.74084148533031</v>
       </c>
       <c r="E7" t="n">
-        <v>204.0417392459941</v>
+        <v>211.3665583296993</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3121057708462645</v>
+        <v>-0.3163593885010391</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7171067098149697</v>
+        <v>0.7169982192117229</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4352291877547695</v>
+        <v>-0.4412275791268334</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7512069581471744</v>
+        <v>0.7511902785850172</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076250953527189</v>
+        <v>1.076091495377691</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.27914456599434</v>
+        <v>10.22371346855337</v>
       </c>
       <c r="E8" t="n">
-        <v>654.540525517875</v>
+        <v>679.5007433040181</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2869601318067684</v>
+        <v>-0.2911624606614568</v>
       </c>
       <c r="G8" t="n">
-        <v>1.176824310076767</v>
+        <v>1.176346980626215</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2438427973909285</v>
+        <v>-0.2475140969941197</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7379395597618746</v>
+        <v>0.7380436567996531</v>
       </c>
       <c r="N8" t="n">
-        <v>1.735012408438913</v>
+        <v>1.734597264664589</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.356492262808532</v>
+        <v>7.366804257686739</v>
       </c>
       <c r="E9" t="n">
-        <v>224.9158832917074</v>
+        <v>229.5175400135861</v>
       </c>
       <c r="F9" t="n">
-        <v>0.424411336498673</v>
+        <v>0.4284342289171192</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4815443749341073</v>
+        <v>0.4815506819605025</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8813545720615008</v>
+        <v>0.8896970660966897</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6787543880674897</v>
+        <v>0.6788365248118184</v>
       </c>
       <c r="N9" t="n">
-        <v>0.653008937724716</v>
+        <v>0.6531130579026951</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.768275834455268</v>
+        <v>6.729511810717589</v>
       </c>
       <c r="E10" t="n">
-        <v>326.7948675360155</v>
+        <v>331.9792814393451</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2575860757166096</v>
+        <v>-0.2637132680030575</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9620176515289415</v>
+        <v>0.9618354251347102</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2677560804702764</v>
+        <v>-0.2741771212742793</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.713646156817675</v>
+        <v>0.7136413907749235</v>
       </c>
       <c r="N10" t="n">
-        <v>1.371627340289989</v>
+        <v>1.371393107653196</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.580451799246024</v>
+        <v>6.598548832274926</v>
       </c>
       <c r="E11" t="n">
-        <v>370.5804213961928</v>
+        <v>396.3304053268983</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9406844128028362</v>
+        <v>0.9507309996343476</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8243498075118239</v>
+        <v>0.8243487572570881</v>
       </c>
       <c r="H11" t="n">
-        <v>1.141122863414199</v>
+        <v>1.153311618734987</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6641779308553243</v>
+        <v>0.6642795132491636</v>
       </c>
       <c r="N11" t="n">
-        <v>1.093871085921587</v>
+        <v>1.094064709273426</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.394276194482449</v>
+        <v>6.321995528369767</v>
       </c>
       <c r="E12" t="n">
-        <v>97.81723656269234</v>
+        <v>100.9669111690087</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2666220996274928</v>
+        <v>-0.2757010190881055</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6610602378797483</v>
+        <v>0.6607883775863485</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4033249685121635</v>
+        <v>-0.4172304302553783</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890753219147589</v>
+        <v>0.7891246923557418</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042148620203791</v>
+        <v>1.041811607384076</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.709280400855604</v>
+        <v>4.691302553247593</v>
       </c>
       <c r="E13" t="n">
-        <v>222.2537858005373</v>
+        <v>231.8776425262494</v>
       </c>
       <c r="F13" t="n">
-        <v>1.748452984952623</v>
+        <v>1.732971103554482</v>
       </c>
       <c r="G13" t="n">
-        <v>0.863905677093221</v>
+        <v>0.8638191239550463</v>
       </c>
       <c r="H13" t="n">
-        <v>2.023893384791305</v>
+        <v>2.006173579047397</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6041260398950588</v>
+        <v>0.6040847323033531</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042711215278432</v>
+        <v>1.042561869761395</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.629563532340897</v>
+        <v>4.601505675734061</v>
       </c>
       <c r="E14" t="n">
-        <v>117.9744394970595</v>
+        <v>123.6406533275792</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.393823299425188</v>
+        <v>-0.3975307347136803</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8533693871506876</v>
+        <v>0.8533720099483474</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4614921807074934</v>
+        <v>-0.4658352161535529</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601559596981815</v>
+        <v>0.7600781509574643</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296014693299492</v>
+        <v>1.295918846567858</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.196433217410772</v>
+        <v>4.250109913844931</v>
       </c>
       <c r="E15" t="n">
-        <v>310.931591013234</v>
+        <v>266.0784620351363</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.01280532735254247</v>
+        <v>0.5893341586862142</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7962286727924539</v>
+        <v>0.9644874930202576</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.01608247453289129</v>
+        <v>0.6110334897560317</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J15" t="n">
         <v>268</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7162359274479307</v>
+        <v>0.5149465579541778</v>
       </c>
       <c r="N15" t="n">
-        <v>1.139368152672856</v>
+        <v>0.992292989190503</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.016186136109154</v>
+        <v>4.156731573806852</v>
       </c>
       <c r="E16" t="n">
-        <v>183.1151341118216</v>
+        <v>328.6609713482976</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4715086229362375</v>
+        <v>-0.02367250179600211</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9605429500828886</v>
+        <v>0.7955383626520648</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4908771886728744</v>
+        <v>-0.0297565810869079</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J16" t="n">
         <v>268</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5160220173154255</v>
+        <v>0.7165681973236933</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9902735566514943</v>
+        <v>1.138937309003035</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.375097111878841</v>
+        <v>3.359845358826696</v>
       </c>
       <c r="E17" t="n">
-        <v>68.18596457916848</v>
+        <v>71.14274318081081</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.211444185004565</v>
+        <v>-0.2173170598896492</v>
       </c>
       <c r="G17" t="n">
-        <v>0.756000084665752</v>
+        <v>0.7559367733086026</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2796880440801143</v>
+        <v>-0.28748047133425</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7245208196716985</v>
+        <v>0.7244514376677967</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094316317376671</v>
+        <v>1.094147605540072</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.117525896858629</v>
+        <v>3.09989987142664</v>
       </c>
       <c r="E18" t="n">
-        <v>66.8952352951906</v>
+        <v>70.31293289642917</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4698284071609558</v>
+        <v>-0.4726388170932567</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7484861811043073</v>
+        <v>0.7484687429489989</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6277048515014355</v>
+        <v>-0.631474355536932</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645374163475918</v>
+        <v>0.7644737662024856</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143280226653874</v>
+        <v>1.143187371158191</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.991420957180464</v>
+        <v>2.974426637831651</v>
       </c>
       <c r="E19" t="n">
-        <v>90.39794395986696</v>
+        <v>92.19790572942391</v>
       </c>
       <c r="F19" t="n">
-        <v>0.127691162378412</v>
+        <v>0.1192402210656878</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4829866484339556</v>
+        <v>0.4829918786974565</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2643782448074706</v>
+        <v>0.2468783147808976</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177111155551203</v>
+        <v>0.7175156420732067</v>
       </c>
       <c r="N19" t="n">
-        <v>0.692556100111647</v>
+        <v>0.6923925155691767</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.590382890754003</v>
+        <v>2.600017143342436</v>
       </c>
       <c r="E20" t="n">
-        <v>96.735542566422</v>
+        <v>102.204194965301</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3230257040484199</v>
+        <v>-0.3194790395123929</v>
       </c>
       <c r="G20" t="n">
-        <v>0.781131138726652</v>
+        <v>0.7811936683464505</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4135358175261006</v>
+        <v>-0.4089626586306477</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7328803653368163</v>
+        <v>0.7329074583220548</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143739706400508</v>
+        <v>1.143902525917503</v>
       </c>
     </row>
   </sheetData>
